--- a/data/EntrevistasRealizadas.xlsx
+++ b/data/EntrevistasRealizadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Autónomo\EAS\web\generator\join tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF367C5-859F-4153-A804-589EB33FF78E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00F186F7-6330-45AD-A961-DD03F954ED91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2624,10 +2624,10 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2678,7 +2678,7 @@
         <xdr:cNvPr id="2" name="Gráfico 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD3C8396-FA72-489D-994F-F536D898174E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52574BB1-4AE6-4B53-9D73-C72C85E5BE91}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3008,31 +3008,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6"/>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4" t="s">
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4" t="s">
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
@@ -3103,7 +3103,7 @@
       <c r="Q3" s="1"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -3156,7 +3156,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
+      <c r="A5" s="4"/>
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
@@ -3207,7 +3207,7 @@
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
+      <c r="A6" s="4"/>
       <c r="B6" s="2" t="s">
         <v>26</v>
       </c>
@@ -3258,7 +3258,7 @@
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
+      <c r="A7" s="4"/>
       <c r="B7" s="2" t="s">
         <v>39</v>
       </c>
@@ -3309,7 +3309,7 @@
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>50</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -3362,7 +3362,7 @@
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
+      <c r="A9" s="4"/>
       <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
@@ -3413,7 +3413,7 @@
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
+      <c r="A10" s="4"/>
       <c r="B10" s="2" t="s">
         <v>26</v>
       </c>
@@ -3464,7 +3464,7 @@
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
+      <c r="A11" s="4"/>
       <c r="B11" s="2" t="s">
         <v>39</v>
       </c>
@@ -3515,7 +3515,7 @@
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
         <v>88</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -3568,7 +3568,7 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
+      <c r="A13" s="4"/>
       <c r="B13" s="2" t="s">
         <v>10</v>
       </c>
@@ -3619,7 +3619,7 @@
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
+      <c r="A14" s="4"/>
       <c r="B14" s="2" t="s">
         <v>26</v>
       </c>
@@ -3670,7 +3670,7 @@
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
+      <c r="A15" s="4"/>
       <c r="B15" s="2" t="s">
         <v>39</v>
       </c>
@@ -3721,7 +3721,7 @@
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>125</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -3774,7 +3774,7 @@
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
+      <c r="A17" s="4"/>
       <c r="B17" s="2" t="s">
         <v>10</v>
       </c>
@@ -3825,7 +3825,7 @@
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
+      <c r="A18" s="4"/>
       <c r="B18" s="2" t="s">
         <v>26</v>
       </c>
@@ -3876,7 +3876,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A19" s="5"/>
+      <c r="A19" s="4"/>
       <c r="B19" s="2" t="s">
         <v>39</v>
       </c>
@@ -3927,7 +3927,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -3980,7 +3980,7 @@
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A21" s="5"/>
+      <c r="A21" s="4"/>
       <c r="B21" s="2" t="s">
         <v>10</v>
       </c>
@@ -4031,7 +4031,7 @@
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="5"/>
+      <c r="A22" s="4"/>
       <c r="B22" s="2" t="s">
         <v>26</v>
       </c>
@@ -4082,7 +4082,7 @@
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" s="5"/>
+      <c r="A23" s="4"/>
       <c r="B23" s="2" t="s">
         <v>39</v>
       </c>
@@ -4240,31 +4240,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6"/>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4" t="s">
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4" t="s">
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
@@ -4335,7 +4335,7 @@
       <c r="Q3" s="1"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>180</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -4388,7 +4388,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
+      <c r="A5" s="4"/>
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
@@ -4439,7 +4439,7 @@
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
+      <c r="A6" s="4"/>
       <c r="B6" s="2" t="s">
         <v>26</v>
       </c>
@@ -4490,7 +4490,7 @@
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
+      <c r="A7" s="4"/>
       <c r="B7" s="2" t="s">
         <v>39</v>
       </c>
@@ -4541,7 +4541,7 @@
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>213</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -4594,7 +4594,7 @@
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
+      <c r="A9" s="4"/>
       <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
@@ -4645,7 +4645,7 @@
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
+      <c r="A10" s="4"/>
       <c r="B10" s="2" t="s">
         <v>26</v>
       </c>
@@ -4696,7 +4696,7 @@
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
+      <c r="A11" s="4"/>
       <c r="B11" s="2" t="s">
         <v>39</v>
       </c>
@@ -4747,7 +4747,7 @@
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
         <v>247</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
+      <c r="A13" s="4"/>
       <c r="B13" s="2" t="s">
         <v>10</v>
       </c>
@@ -4851,7 +4851,7 @@
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
+      <c r="A14" s="4"/>
       <c r="B14" s="2" t="s">
         <v>26</v>
       </c>
@@ -4902,7 +4902,7 @@
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
+      <c r="A15" s="4"/>
       <c r="B15" s="2" t="s">
         <v>39</v>
       </c>
@@ -4953,7 +4953,7 @@
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>281</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -5006,7 +5006,7 @@
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
+      <c r="A17" s="4"/>
       <c r="B17" s="2" t="s">
         <v>10</v>
       </c>
@@ -5057,7 +5057,7 @@
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
+      <c r="A18" s="4"/>
       <c r="B18" s="2" t="s">
         <v>26</v>
       </c>
@@ -5108,7 +5108,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A19" s="5"/>
+      <c r="A19" s="4"/>
       <c r="B19" s="2" t="s">
         <v>39</v>
       </c>
@@ -5159,7 +5159,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -5212,7 +5212,7 @@
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A21" s="5"/>
+      <c r="A21" s="4"/>
       <c r="B21" s="2" t="s">
         <v>10</v>
       </c>
@@ -5263,7 +5263,7 @@
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="5"/>
+      <c r="A22" s="4"/>
       <c r="B22" s="2" t="s">
         <v>26</v>
       </c>
@@ -5314,7 +5314,7 @@
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" s="5"/>
+      <c r="A23" s="4"/>
       <c r="B23" s="2" t="s">
         <v>39</v>
       </c>
@@ -5472,31 +5472,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6"/>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4" t="s">
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4" t="s">
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
@@ -5567,7 +5567,7 @@
       <c r="Q3" s="1"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>312</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -5620,7 +5620,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
+      <c r="A5" s="4"/>
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
@@ -5671,7 +5671,7 @@
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
+      <c r="A6" s="4"/>
       <c r="B6" s="2" t="s">
         <v>26</v>
       </c>
@@ -5722,7 +5722,7 @@
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
+      <c r="A7" s="4"/>
       <c r="B7" s="2" t="s">
         <v>39</v>
       </c>
@@ -5773,7 +5773,7 @@
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>344</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
+      <c r="A9" s="4"/>
       <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
@@ -5877,7 +5877,7 @@
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
+      <c r="A10" s="4"/>
       <c r="B10" s="2" t="s">
         <v>26</v>
       </c>
@@ -5928,7 +5928,7 @@
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
+      <c r="A11" s="4"/>
       <c r="B11" s="2" t="s">
         <v>39</v>
       </c>
@@ -5979,7 +5979,7 @@
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
         <v>377</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -6032,7 +6032,7 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
+      <c r="A13" s="4"/>
       <c r="B13" s="2" t="s">
         <v>10</v>
       </c>
@@ -6083,7 +6083,7 @@
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
+      <c r="A14" s="4"/>
       <c r="B14" s="2" t="s">
         <v>26</v>
       </c>
@@ -6134,7 +6134,7 @@
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
+      <c r="A15" s="4"/>
       <c r="B15" s="2" t="s">
         <v>39</v>
       </c>
@@ -6185,7 +6185,7 @@
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>412</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -6238,7 +6238,7 @@
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
+      <c r="A17" s="4"/>
       <c r="B17" s="2" t="s">
         <v>10</v>
       </c>
@@ -6289,7 +6289,7 @@
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
+      <c r="A18" s="4"/>
       <c r="B18" s="2" t="s">
         <v>26</v>
       </c>
@@ -6340,7 +6340,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A19" s="5"/>
+      <c r="A19" s="4"/>
       <c r="B19" s="2" t="s">
         <v>39</v>
       </c>
@@ -6391,7 +6391,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="4" t="s">
         <v>445</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -6444,7 +6444,7 @@
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A21" s="5"/>
+      <c r="A21" s="4"/>
       <c r="B21" s="2" t="s">
         <v>10</v>
       </c>
@@ -6495,7 +6495,7 @@
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="5"/>
+      <c r="A22" s="4"/>
       <c r="B22" s="2" t="s">
         <v>26</v>
       </c>
@@ -6546,7 +6546,7 @@
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" s="5"/>
+      <c r="A23" s="4"/>
       <c r="B23" s="2" t="s">
         <v>39</v>
       </c>
@@ -6597,7 +6597,7 @@
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="4" t="s">
         <v>472</v>
       </c>
       <c r="B24" s="2" t="s">
@@ -6650,7 +6650,7 @@
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A25" s="5"/>
+      <c r="A25" s="4"/>
       <c r="B25" s="2" t="s">
         <v>10</v>
       </c>
@@ -6701,7 +6701,7 @@
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A26" s="5"/>
+      <c r="A26" s="4"/>
       <c r="B26" s="2" t="s">
         <v>26</v>
       </c>
@@ -6752,7 +6752,7 @@
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A27" s="5"/>
+      <c r="A27" s="4"/>
       <c r="B27" s="2" t="s">
         <v>39</v>
       </c>
@@ -6803,7 +6803,7 @@
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="4" t="s">
         <v>503</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -6856,7 +6856,7 @@
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A29" s="5"/>
+      <c r="A29" s="4"/>
       <c r="B29" s="2" t="s">
         <v>10</v>
       </c>
@@ -6907,7 +6907,7 @@
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A30" s="5"/>
+      <c r="A30" s="4"/>
       <c r="B30" s="2" t="s">
         <v>26</v>
       </c>
@@ -6958,7 +6958,7 @@
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A31" s="5"/>
+      <c r="A31" s="4"/>
       <c r="B31" s="2" t="s">
         <v>39</v>
       </c>
@@ -7009,7 +7009,7 @@
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="4" t="s">
         <v>529</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -7062,7 +7062,7 @@
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A33" s="5"/>
+      <c r="A33" s="4"/>
       <c r="B33" s="2" t="s">
         <v>10</v>
       </c>
@@ -7113,7 +7113,7 @@
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A34" s="5"/>
+      <c r="A34" s="4"/>
       <c r="B34" s="2" t="s">
         <v>26</v>
       </c>
@@ -7164,7 +7164,7 @@
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A35" s="5"/>
+      <c r="A35" s="4"/>
       <c r="B35" s="2" t="s">
         <v>39</v>
       </c>
@@ -7215,7 +7215,7 @@
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B36" s="2" t="s">
@@ -7268,7 +7268,7 @@
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A37" s="5"/>
+      <c r="A37" s="4"/>
       <c r="B37" s="2" t="s">
         <v>10</v>
       </c>
@@ -7319,7 +7319,7 @@
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A38" s="5"/>
+      <c r="A38" s="4"/>
       <c r="B38" s="2" t="s">
         <v>26</v>
       </c>
@@ -7370,7 +7370,7 @@
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A39" s="5"/>
+      <c r="A39" s="4"/>
       <c r="B39" s="2" t="s">
         <v>39</v>
       </c>
@@ -7532,31 +7532,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6"/>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4" t="s">
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4" t="s">
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
@@ -7627,7 +7627,7 @@
       <c r="Q3" s="1"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>555</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -7680,7 +7680,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
+      <c r="A5" s="4"/>
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
@@ -7731,7 +7731,7 @@
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
+      <c r="A6" s="4"/>
       <c r="B6" s="2" t="s">
         <v>26</v>
       </c>
@@ -7782,7 +7782,7 @@
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
+      <c r="A7" s="4"/>
       <c r="B7" s="2" t="s">
         <v>39</v>
       </c>
@@ -7833,7 +7833,7 @@
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>590</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -7886,7 +7886,7 @@
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
+      <c r="A9" s="4"/>
       <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
@@ -7937,7 +7937,7 @@
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
+      <c r="A10" s="4"/>
       <c r="B10" s="2" t="s">
         <v>26</v>
       </c>
@@ -7988,7 +7988,7 @@
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
+      <c r="A11" s="4"/>
       <c r="B11" s="2" t="s">
         <v>39</v>
       </c>
@@ -8039,7 +8039,7 @@
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
         <v>621</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -8092,7 +8092,7 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
+      <c r="A13" s="4"/>
       <c r="B13" s="2" t="s">
         <v>10</v>
       </c>
@@ -8143,7 +8143,7 @@
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
+      <c r="A14" s="4"/>
       <c r="B14" s="2" t="s">
         <v>26</v>
       </c>
@@ -8194,7 +8194,7 @@
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
+      <c r="A15" s="4"/>
       <c r="B15" s="2" t="s">
         <v>39</v>
       </c>
@@ -8245,7 +8245,7 @@
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -8298,7 +8298,7 @@
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
+      <c r="A17" s="4"/>
       <c r="B17" s="2" t="s">
         <v>10</v>
       </c>
@@ -8349,7 +8349,7 @@
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
+      <c r="A18" s="4"/>
       <c r="B18" s="2" t="s">
         <v>26</v>
       </c>
@@ -8400,7 +8400,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A19" s="5"/>
+      <c r="A19" s="4"/>
       <c r="B19" s="2" t="s">
         <v>39</v>
       </c>
@@ -8557,31 +8557,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6"/>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4" t="s">
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4" t="s">
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
@@ -8652,7 +8652,7 @@
       <c r="Q3" s="1"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>654</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -8705,7 +8705,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
+      <c r="A5" s="4"/>
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
@@ -8756,7 +8756,7 @@
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
+      <c r="A6" s="4"/>
       <c r="B6" s="2" t="s">
         <v>26</v>
       </c>
@@ -8807,7 +8807,7 @@
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
+      <c r="A7" s="4"/>
       <c r="B7" s="2" t="s">
         <v>39</v>
       </c>
@@ -8858,7 +8858,7 @@
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>686</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -8911,7 +8911,7 @@
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
+      <c r="A9" s="4"/>
       <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
@@ -8962,7 +8962,7 @@
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
+      <c r="A10" s="4"/>
       <c r="B10" s="2" t="s">
         <v>26</v>
       </c>
@@ -9013,7 +9013,7 @@
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
+      <c r="A11" s="4"/>
       <c r="B11" s="2" t="s">
         <v>39</v>
       </c>
@@ -9064,7 +9064,7 @@
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
         <v>715</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -9117,7 +9117,7 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
+      <c r="A13" s="4"/>
       <c r="B13" s="2" t="s">
         <v>10</v>
       </c>
@@ -9168,7 +9168,7 @@
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
+      <c r="A14" s="4"/>
       <c r="B14" s="2" t="s">
         <v>26</v>
       </c>
@@ -9219,7 +9219,7 @@
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
+      <c r="A15" s="4"/>
       <c r="B15" s="2" t="s">
         <v>39</v>
       </c>
@@ -9270,7 +9270,7 @@
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>745</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -9323,7 +9323,7 @@
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
+      <c r="A17" s="4"/>
       <c r="B17" s="2" t="s">
         <v>10</v>
       </c>
@@ -9374,7 +9374,7 @@
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
+      <c r="A18" s="4"/>
       <c r="B18" s="2" t="s">
         <v>26</v>
       </c>
@@ -9425,7 +9425,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A19" s="5"/>
+      <c r="A19" s="4"/>
       <c r="B19" s="2" t="s">
         <v>39</v>
       </c>
@@ -9476,7 +9476,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="4" t="s">
         <v>774</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -9529,7 +9529,7 @@
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A21" s="5"/>
+      <c r="A21" s="4"/>
       <c r="B21" s="2" t="s">
         <v>10</v>
       </c>
@@ -9580,7 +9580,7 @@
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="5"/>
+      <c r="A22" s="4"/>
       <c r="B22" s="2" t="s">
         <v>26</v>
       </c>
@@ -9631,7 +9631,7 @@
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" s="5"/>
+      <c r="A23" s="4"/>
       <c r="B23" s="2" t="s">
         <v>39</v>
       </c>
@@ -9682,7 +9682,7 @@
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="4" t="s">
         <v>802</v>
       </c>
       <c r="B24" s="2" t="s">
@@ -9735,7 +9735,7 @@
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A25" s="5"/>
+      <c r="A25" s="4"/>
       <c r="B25" s="2" t="s">
         <v>10</v>
       </c>
@@ -9786,7 +9786,7 @@
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A26" s="5"/>
+      <c r="A26" s="4"/>
       <c r="B26" s="2" t="s">
         <v>26</v>
       </c>
@@ -9837,7 +9837,7 @@
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A27" s="5"/>
+      <c r="A27" s="4"/>
       <c r="B27" s="2" t="s">
         <v>39</v>
       </c>
@@ -9888,7 +9888,7 @@
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -9941,7 +9941,7 @@
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A29" s="5"/>
+      <c r="A29" s="4"/>
       <c r="B29" s="2" t="s">
         <v>10</v>
       </c>
@@ -9992,7 +9992,7 @@
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A30" s="5"/>
+      <c r="A30" s="4"/>
       <c r="B30" s="2" t="s">
         <v>26</v>
       </c>
@@ -10043,7 +10043,7 @@
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A31" s="5"/>
+      <c r="A31" s="4"/>
       <c r="B31" s="2" t="s">
         <v>39</v>
       </c>
@@ -10195,7 +10195,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A06D6D35-4E0C-4C9F-94D2-63DF1DA32A5B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94CBF94-6F84-4122-A98A-43DFFF11C3E7}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>

--- a/data/EntrevistasRealizadas.xlsx
+++ b/data/EntrevistasRealizadas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Autónomo\EAS\web\generator\join tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00F186F7-6330-45AD-A961-DD03F954ED91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F93A3B-D050-4E44-9797-D1158BED2619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,12 +30,12 @@
     <t>Tamaños muestrales en cada edición (entrevistas realizadas)*</t>
   </si>
   <si>
+    <t>Niño</t>
+  </si>
+  <si>
     <t>Niña</t>
   </si>
   <si>
-    <t>Niño</t>
-  </si>
-  <si>
     <t>Total</t>
   </si>
   <si>
@@ -60,6 +60,21 @@
     <t>% (columna)</t>
   </si>
   <si>
+    <t>16,76%</t>
+  </si>
+  <si>
+    <t>19,27%</t>
+  </si>
+  <si>
+    <t>17,56%</t>
+  </si>
+  <si>
+    <t>11,87%</t>
+  </si>
+  <si>
+    <t>16,47%</t>
+  </si>
+  <si>
     <t>15,91%</t>
   </si>
   <si>
@@ -75,21 +90,6 @@
     <t>17,32%</t>
   </si>
   <si>
-    <t>16,76%</t>
-  </si>
-  <si>
-    <t>19,27%</t>
-  </si>
-  <si>
-    <t>17,56%</t>
-  </si>
-  <si>
-    <t>11,87%</t>
-  </si>
-  <si>
-    <t>16,47%</t>
-  </si>
-  <si>
     <t>16,35%</t>
   </si>
   <si>
@@ -108,6 +108,18 @@
     <t>% (fila)</t>
   </si>
   <si>
+    <t>26,3%</t>
+  </si>
+  <si>
+    <t>29,91%</t>
+  </si>
+  <si>
+    <t>27,02%</t>
+  </si>
+  <si>
+    <t>100,0%</t>
+  </si>
+  <si>
     <t>23,11%</t>
   </si>
   <si>
@@ -120,18 +132,6 @@
     <t>15,55%</t>
   </si>
   <si>
-    <t>100,0%</t>
-  </si>
-  <si>
-    <t>26,3%</t>
-  </si>
-  <si>
-    <t>29,91%</t>
-  </si>
-  <si>
-    <t>27,02%</t>
-  </si>
-  <si>
     <t>24,69%</t>
   </si>
   <si>
@@ -147,6 +147,21 @@
     <t>% (edición)</t>
   </si>
   <si>
+    <t>52,91%</t>
+  </si>
+  <si>
+    <t>48,59%</t>
+  </si>
+  <si>
+    <t>46,98%</t>
+  </si>
+  <si>
+    <t>51,56%</t>
+  </si>
+  <si>
+    <t>49,68%</t>
+  </si>
+  <si>
     <t>47,09%</t>
   </si>
   <si>
@@ -162,24 +177,24 @@
     <t>50,32%</t>
   </si>
   <si>
-    <t>52,91%</t>
-  </si>
-  <si>
-    <t>48,59%</t>
-  </si>
-  <si>
-    <t>46,98%</t>
-  </si>
-  <si>
-    <t>51,56%</t>
-  </si>
-  <si>
-    <t>49,68%</t>
-  </si>
-  <si>
     <t>3-7</t>
   </si>
   <si>
+    <t>35,17%</t>
+  </si>
+  <si>
+    <t>34,82%</t>
+  </si>
+  <si>
+    <t>35,68%</t>
+  </si>
+  <si>
+    <t>28,25%</t>
+  </si>
+  <si>
+    <t>33,6%</t>
+  </si>
+  <si>
     <t>37,23%</t>
   </si>
   <si>
@@ -195,21 +210,6 @@
     <t>32,34%</t>
   </si>
   <si>
-    <t>35,17%</t>
-  </si>
-  <si>
-    <t>34,82%</t>
-  </si>
-  <si>
-    <t>35,68%</t>
-  </si>
-  <si>
-    <t>28,25%</t>
-  </si>
-  <si>
-    <t>33,6%</t>
-  </si>
-  <si>
     <t>36,17%</t>
   </si>
   <si>
@@ -225,6 +225,18 @@
     <t>32,99%</t>
   </si>
   <si>
+    <t>27,05%</t>
+  </si>
+  <si>
+    <t>26,49%</t>
+  </si>
+  <si>
+    <t>26,91%</t>
+  </si>
+  <si>
+    <t>19,55%</t>
+  </si>
+  <si>
     <t>28,95%</t>
   </si>
   <si>
@@ -237,18 +249,6 @@
     <t>19,71%</t>
   </si>
   <si>
-    <t>27,05%</t>
-  </si>
-  <si>
-    <t>26,49%</t>
-  </si>
-  <si>
-    <t>26,91%</t>
-  </si>
-  <si>
-    <t>19,55%</t>
-  </si>
-  <si>
     <t>27,97%</t>
   </si>
   <si>
@@ -261,6 +261,21 @@
     <t>19,63%</t>
   </si>
   <si>
+    <t>50,2%</t>
+  </si>
+  <si>
+    <t>52,38%</t>
+  </si>
+  <si>
+    <t>53,37%</t>
+  </si>
+  <si>
+    <t>51,69%</t>
+  </si>
+  <si>
+    <t>51,89%</t>
+  </si>
+  <si>
     <t>49,8%</t>
   </si>
   <si>
@@ -276,24 +291,21 @@
     <t>48,11%</t>
   </si>
   <si>
-    <t>50,2%</t>
-  </si>
-  <si>
-    <t>52,38%</t>
-  </si>
-  <si>
-    <t>53,37%</t>
-  </si>
-  <si>
-    <t>51,69%</t>
-  </si>
-  <si>
-    <t>51,89%</t>
-  </si>
-  <si>
     <t>8-11</t>
   </si>
   <si>
+    <t>19,52%</t>
+  </si>
+  <si>
+    <t>21,23%</t>
+  </si>
+  <si>
+    <t>24,87%</t>
+  </si>
+  <si>
+    <t>22,51%</t>
+  </si>
+  <si>
     <t>18,76%</t>
   </si>
   <si>
@@ -309,18 +321,6 @@
     <t>22,73%</t>
   </si>
   <si>
-    <t>19,52%</t>
-  </si>
-  <si>
-    <t>21,23%</t>
-  </si>
-  <si>
-    <t>24,87%</t>
-  </si>
-  <si>
-    <t>22,51%</t>
-  </si>
-  <si>
     <t>19,15%</t>
   </si>
   <si>
@@ -336,6 +336,18 @@
     <t>22,62%</t>
   </si>
   <si>
+    <t>22,41%</t>
+  </si>
+  <si>
+    <t>24,1%</t>
+  </si>
+  <si>
+    <t>27,8%</t>
+  </si>
+  <si>
+    <t>25,69%</t>
+  </si>
+  <si>
     <t>20,76%</t>
   </si>
   <si>
@@ -348,18 +360,6 @@
     <t>25,43%</t>
   </si>
   <si>
-    <t>22,41%</t>
-  </si>
-  <si>
-    <t>24,1%</t>
-  </si>
-  <si>
-    <t>27,8%</t>
-  </si>
-  <si>
-    <t>25,69%</t>
-  </si>
-  <si>
     <t>21,6%</t>
   </si>
   <si>
@@ -372,6 +372,21 @@
     <t>25,56%</t>
   </si>
   <si>
+    <t>52,61%</t>
+  </si>
+  <si>
+    <t>50,55%</t>
+  </si>
+  <si>
+    <t>49,16%</t>
+  </si>
+  <si>
+    <t>50,94%</t>
+  </si>
+  <si>
+    <t>50,7%</t>
+  </si>
+  <si>
     <t>47,39%</t>
   </si>
   <si>
@@ -387,24 +402,24 @@
     <t>49,3%</t>
   </si>
   <si>
-    <t>52,61%</t>
-  </si>
-  <si>
-    <t>50,55%</t>
-  </si>
-  <si>
-    <t>49,16%</t>
-  </si>
-  <si>
-    <t>50,94%</t>
-  </si>
-  <si>
-    <t>50,7%</t>
-  </si>
-  <si>
     <t>12-15</t>
   </si>
   <si>
+    <t>28,55%</t>
+  </si>
+  <si>
+    <t>24,67%</t>
+  </si>
+  <si>
+    <t>22,07%</t>
+  </si>
+  <si>
+    <t>35,01%</t>
+  </si>
+  <si>
+    <t>27,42%</t>
+  </si>
+  <si>
     <t>28,09%</t>
   </si>
   <si>
@@ -420,21 +435,6 @@
     <t>27,6%</t>
   </si>
   <si>
-    <t>28,55%</t>
-  </si>
-  <si>
-    <t>24,67%</t>
-  </si>
-  <si>
-    <t>22,07%</t>
-  </si>
-  <si>
-    <t>35,01%</t>
-  </si>
-  <si>
-    <t>27,42%</t>
-  </si>
-  <si>
     <t>28,33%</t>
   </si>
   <si>
@@ -447,6 +447,15 @@
     <t>27,51%</t>
   </si>
   <si>
+    <t>23,0%</t>
+  </si>
+  <si>
+    <t>20,4%</t>
+  </si>
+  <si>
+    <t>29,69%</t>
+  </si>
+  <si>
     <t>25,6%</t>
   </si>
   <si>
@@ -459,15 +468,6 @@
     <t>30,62%</t>
   </si>
   <si>
-    <t>23,0%</t>
-  </si>
-  <si>
-    <t>20,4%</t>
-  </si>
-  <si>
-    <t>29,69%</t>
-  </si>
-  <si>
     <t>26,27%</t>
   </si>
   <si>
@@ -480,6 +480,21 @@
     <t>30,15%</t>
   </si>
   <si>
+    <t>52,01%</t>
+  </si>
+  <si>
+    <t>52,17%</t>
+  </si>
+  <si>
+    <t>48,86%</t>
+  </si>
+  <si>
+    <t>50,0%</t>
+  </si>
+  <si>
+    <t>50,77%</t>
+  </si>
+  <si>
     <t>47,99%</t>
   </si>
   <si>
@@ -489,22 +504,16 @@
     <t>51,14%</t>
   </si>
   <si>
-    <t>50,0%</t>
-  </si>
-  <si>
     <t>49,23%</t>
   </si>
   <si>
-    <t>52,01%</t>
-  </si>
-  <si>
-    <t>52,17%</t>
-  </si>
-  <si>
-    <t>48,86%</t>
-  </si>
-  <si>
-    <t>50,77%</t>
+    <t>25,84%</t>
+  </si>
+  <si>
+    <t>25,35%</t>
+  </si>
+  <si>
+    <t>23,25%</t>
   </si>
   <si>
     <t>25,15%</t>
@@ -519,15 +528,6 @@
     <t>23,3%</t>
   </si>
   <si>
-    <t>25,84%</t>
-  </si>
-  <si>
-    <t>25,35%</t>
-  </si>
-  <si>
-    <t>23,25%</t>
-  </si>
-  <si>
     <t>25,51%</t>
   </si>
   <si>
@@ -540,6 +540,18 @@
     <t>23,28%</t>
   </si>
   <si>
+    <t>51,62%</t>
+  </si>
+  <si>
+    <t>51,17%</t>
+  </si>
+  <si>
+    <t>50,09%</t>
+  </si>
+  <si>
+    <t>50,89%</t>
+  </si>
+  <si>
     <t>48,38%</t>
   </si>
   <si>
@@ -552,24 +564,27 @@
     <t>49,11%</t>
   </si>
   <si>
-    <t>51,62%</t>
-  </si>
-  <si>
-    <t>51,17%</t>
-  </si>
-  <si>
-    <t>50,09%</t>
-  </si>
-  <si>
-    <t>50,89%</t>
-  </si>
-  <si>
     <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
   </si>
   <si>
     <t>&lt;10.000 hab</t>
   </si>
   <si>
+    <t>20,81%</t>
+  </si>
+  <si>
+    <t>19,65%</t>
+  </si>
+  <si>
+    <t>18,31%</t>
+  </si>
+  <si>
+    <t>17,5%</t>
+  </si>
+  <si>
+    <t>19,11%</t>
+  </si>
+  <si>
     <t>19,94%</t>
   </si>
   <si>
@@ -582,21 +597,6 @@
     <t>20,78%</t>
   </si>
   <si>
-    <t>20,81%</t>
-  </si>
-  <si>
-    <t>19,65%</t>
-  </si>
-  <si>
-    <t>18,31%</t>
-  </si>
-  <si>
-    <t>17,5%</t>
-  </si>
-  <si>
-    <t>19,11%</t>
-  </si>
-  <si>
     <t>20,39%</t>
   </si>
   <si>
@@ -609,6 +609,18 @@
     <t>19,13%</t>
   </si>
   <si>
+    <t>28,14%</t>
+  </si>
+  <si>
+    <t>26,28%</t>
+  </si>
+  <si>
+    <t>24,28%</t>
+  </si>
+  <si>
+    <t>21,3%</t>
+  </si>
+  <si>
     <t>26,19%</t>
   </si>
   <si>
@@ -621,18 +633,6 @@
     <t>25,29%</t>
   </si>
   <si>
-    <t>28,14%</t>
-  </si>
-  <si>
-    <t>26,28%</t>
-  </si>
-  <si>
-    <t>24,28%</t>
-  </si>
-  <si>
-    <t>21,3%</t>
-  </si>
-  <si>
     <t>27,19%</t>
   </si>
   <si>
@@ -642,6 +642,18 @@
     <t>23,26%</t>
   </si>
   <si>
+    <t>52,68%</t>
+  </si>
+  <si>
+    <t>52,75%</t>
+  </si>
+  <si>
+    <t>51,05%</t>
+  </si>
+  <si>
+    <t>46,59%</t>
+  </si>
+  <si>
     <t>47,32%</t>
   </si>
   <si>
@@ -654,21 +666,24 @@
     <t>53,41%</t>
   </si>
   <si>
-    <t>52,68%</t>
-  </si>
-  <si>
-    <t>52,75%</t>
-  </si>
-  <si>
-    <t>51,05%</t>
-  </si>
-  <si>
-    <t>46,59%</t>
-  </si>
-  <si>
     <t>10-50.000 hab</t>
   </si>
   <si>
+    <t>29,65%</t>
+  </si>
+  <si>
+    <t>30,17%</t>
+  </si>
+  <si>
+    <t>31,17%</t>
+  </si>
+  <si>
+    <t>35,11%</t>
+  </si>
+  <si>
+    <t>31,44%</t>
+  </si>
+  <si>
     <t>30,65%</t>
   </si>
   <si>
@@ -681,21 +696,6 @@
     <t>30,76%</t>
   </si>
   <si>
-    <t>29,65%</t>
-  </si>
-  <si>
-    <t>30,17%</t>
-  </si>
-  <si>
-    <t>31,17%</t>
-  </si>
-  <si>
-    <t>35,11%</t>
-  </si>
-  <si>
-    <t>31,44%</t>
-  </si>
-  <si>
     <t>30,13%</t>
   </si>
   <si>
@@ -711,6 +711,15 @@
     <t>31,11%</t>
   </si>
   <si>
+    <t>24,38%</t>
+  </si>
+  <si>
+    <t>24,53%</t>
+  </si>
+  <si>
+    <t>25,13%</t>
+  </si>
+  <si>
     <t>25,06%</t>
   </si>
   <si>
@@ -723,21 +732,27 @@
     <t>22,49%</t>
   </si>
   <si>
-    <t>24,38%</t>
-  </si>
-  <si>
-    <t>24,53%</t>
-  </si>
-  <si>
-    <t>25,13%</t>
-  </si>
-  <si>
     <t>24,71%</t>
   </si>
   <si>
     <t>25,95%</t>
   </si>
   <si>
+    <t>50,79%</t>
+  </si>
+  <si>
+    <t>50,39%</t>
+  </si>
+  <si>
+    <t>49,85%</t>
+  </si>
+  <si>
+    <t>55,06%</t>
+  </si>
+  <si>
+    <t>51,48%</t>
+  </si>
+  <si>
     <t>49,21%</t>
   </si>
   <si>
@@ -753,24 +768,24 @@
     <t>48,52%</t>
   </si>
   <si>
-    <t>50,79%</t>
-  </si>
-  <si>
-    <t>50,39%</t>
-  </si>
-  <si>
-    <t>49,85%</t>
-  </si>
-  <si>
-    <t>55,06%</t>
-  </si>
-  <si>
-    <t>51,48%</t>
-  </si>
-  <si>
     <t>&gt;50.000 hab</t>
   </si>
   <si>
+    <t>21,36%</t>
+  </si>
+  <si>
+    <t>23,84%</t>
+  </si>
+  <si>
+    <t>23,29%</t>
+  </si>
+  <si>
+    <t>23,03%</t>
+  </si>
+  <si>
+    <t>22,87%</t>
+  </si>
+  <si>
     <t>22,5%</t>
   </si>
   <si>
@@ -786,21 +801,6 @@
     <t>23,65%</t>
   </si>
   <si>
-    <t>21,36%</t>
-  </si>
-  <si>
-    <t>23,84%</t>
-  </si>
-  <si>
-    <t>23,29%</t>
-  </si>
-  <si>
-    <t>23,03%</t>
-  </si>
-  <si>
-    <t>22,87%</t>
-  </si>
-  <si>
     <t>21,91%</t>
   </si>
   <si>
@@ -813,6 +813,18 @@
     <t>23,54%</t>
   </si>
   <si>
+    <t>24,14%</t>
+  </si>
+  <si>
+    <t>26,64%</t>
+  </si>
+  <si>
+    <t>25,81%</t>
+  </si>
+  <si>
+    <t>23,41%</t>
+  </si>
+  <si>
     <t>23,93%</t>
   </si>
   <si>
@@ -822,18 +834,6 @@
     <t>23,72%</t>
   </si>
   <si>
-    <t>24,14%</t>
-  </si>
-  <si>
-    <t>26,64%</t>
-  </si>
-  <si>
-    <t>25,81%</t>
-  </si>
-  <si>
-    <t>23,41%</t>
-  </si>
-  <si>
     <t>24,04%</t>
   </si>
   <si>
@@ -846,6 +846,18 @@
     <t>23,57%</t>
   </si>
   <si>
+    <t>50,33%</t>
+  </si>
+  <si>
+    <t>48,92%</t>
+  </si>
+  <si>
+    <t>49,78%</t>
+  </si>
+  <si>
+    <t>50,1%</t>
+  </si>
+  <si>
     <t>49,67%</t>
   </si>
   <si>
@@ -858,21 +870,24 @@
     <t>49,9%</t>
   </si>
   <si>
-    <t>50,33%</t>
-  </si>
-  <si>
-    <t>48,92%</t>
-  </si>
-  <si>
-    <t>49,78%</t>
-  </si>
-  <si>
-    <t>50,1%</t>
-  </si>
-  <si>
     <t>Capitales</t>
   </si>
   <si>
+    <t>28,18%</t>
+  </si>
+  <si>
+    <t>26,35%</t>
+  </si>
+  <si>
+    <t>27,23%</t>
+  </si>
+  <si>
+    <t>24,36%</t>
+  </si>
+  <si>
+    <t>26,58%</t>
+  </si>
+  <si>
     <t>26,92%</t>
   </si>
   <si>
@@ -882,21 +897,6 @@
     <t>26,44%</t>
   </si>
   <si>
-    <t>28,18%</t>
-  </si>
-  <si>
-    <t>26,35%</t>
-  </si>
-  <si>
-    <t>27,23%</t>
-  </si>
-  <si>
-    <t>24,36%</t>
-  </si>
-  <si>
-    <t>26,58%</t>
-  </si>
-  <si>
     <t>27,57%</t>
   </si>
   <si>
@@ -909,6 +909,15 @@
     <t>26,51%</t>
   </si>
   <si>
+    <t>27,39%</t>
+  </si>
+  <si>
+    <t>25,34%</t>
+  </si>
+  <si>
+    <t>21,31%</t>
+  </si>
+  <si>
     <t>25,61%</t>
   </si>
   <si>
@@ -921,15 +930,6 @@
     <t>22,43%</t>
   </si>
   <si>
-    <t>27,39%</t>
-  </si>
-  <si>
-    <t>25,34%</t>
-  </si>
-  <si>
-    <t>21,31%</t>
-  </si>
-  <si>
     <t>26,52%</t>
   </si>
   <si>
@@ -939,6 +939,18 @@
     <t>21,86%</t>
   </si>
   <si>
+    <t>52,76%</t>
+  </si>
+  <si>
+    <t>50,72%</t>
+  </si>
+  <si>
+    <t>49,79%</t>
+  </si>
+  <si>
+    <t>51,07%</t>
+  </si>
+  <si>
     <t>47,24%</t>
   </si>
   <si>
@@ -951,21 +963,24 @@
     <t>48,93%</t>
   </si>
   <si>
-    <t>52,76%</t>
-  </si>
-  <si>
-    <t>50,72%</t>
-  </si>
-  <si>
-    <t>49,79%</t>
-  </si>
-  <si>
-    <t>51,07%</t>
-  </si>
-  <si>
     <t>Almería</t>
   </si>
   <si>
+    <t>7,83%</t>
+  </si>
+  <si>
+    <t>8,29%</t>
+  </si>
+  <si>
+    <t>8,64%</t>
+  </si>
+  <si>
+    <t>10,44%</t>
+  </si>
+  <si>
+    <t>8,76%</t>
+  </si>
+  <si>
     <t>8,35%</t>
   </si>
   <si>
@@ -981,21 +996,6 @@
     <t>8,94%</t>
   </si>
   <si>
-    <t>7,83%</t>
-  </si>
-  <si>
-    <t>8,29%</t>
-  </si>
-  <si>
-    <t>8,64%</t>
-  </si>
-  <si>
-    <t>10,44%</t>
-  </si>
-  <si>
-    <t>8,76%</t>
-  </si>
-  <si>
     <t>8,08%</t>
   </si>
   <si>
@@ -1011,30 +1011,42 @@
     <t>8,85%</t>
   </si>
   <si>
+    <t>23,1%</t>
+  </si>
+  <si>
+    <t>24,18%</t>
+  </si>
+  <si>
+    <t>25,0%</t>
+  </si>
+  <si>
+    <t>27,72%</t>
+  </si>
+  <si>
     <t>23,48%</t>
   </si>
   <si>
     <t>24,31%</t>
   </si>
   <si>
-    <t>23,1%</t>
-  </si>
-  <si>
-    <t>24,18%</t>
-  </si>
-  <si>
-    <t>25,0%</t>
-  </si>
-  <si>
-    <t>27,72%</t>
-  </si>
-  <si>
     <t>24,25%</t>
   </si>
   <si>
     <t>27,12%</t>
   </si>
   <si>
+    <t>50,28%</t>
+  </si>
+  <si>
+    <t>49,73%</t>
+  </si>
+  <si>
+    <t>51,52%</t>
+  </si>
+  <si>
+    <t>50,41%</t>
+  </si>
+  <si>
     <t>49,72%</t>
   </si>
   <si>
@@ -1047,21 +1059,24 @@
     <t>49,59%</t>
   </si>
   <si>
-    <t>50,28%</t>
-  </si>
-  <si>
-    <t>49,73%</t>
-  </si>
-  <si>
-    <t>51,52%</t>
-  </si>
-  <si>
-    <t>50,41%</t>
-  </si>
-  <si>
     <t>Cádiz</t>
   </si>
   <si>
+    <t>15,1%</t>
+  </si>
+  <si>
+    <t>15,36%</t>
+  </si>
+  <si>
+    <t>15,12%</t>
+  </si>
+  <si>
+    <t>15,97%</t>
+  </si>
+  <si>
+    <t>15,37%</t>
+  </si>
+  <si>
     <t>15,32%</t>
   </si>
   <si>
@@ -1077,21 +1092,6 @@
     <t>15,0%</t>
   </si>
   <si>
-    <t>15,1%</t>
-  </si>
-  <si>
-    <t>15,36%</t>
-  </si>
-  <si>
-    <t>15,12%</t>
-  </si>
-  <si>
-    <t>15,97%</t>
-  </si>
-  <si>
-    <t>15,37%</t>
-  </si>
-  <si>
     <t>15,21%</t>
   </si>
   <si>
@@ -1104,6 +1104,18 @@
     <t>15,19%</t>
   </si>
   <si>
+    <t>25,39%</t>
+  </si>
+  <si>
+    <t>25,54%</t>
+  </si>
+  <si>
+    <t>24,92%</t>
+  </si>
+  <si>
+    <t>24,15%</t>
+  </si>
+  <si>
     <t>25,04%</t>
   </si>
   <si>
@@ -1113,18 +1125,6 @@
     <t>23,39%</t>
   </si>
   <si>
-    <t>25,39%</t>
-  </si>
-  <si>
-    <t>25,54%</t>
-  </si>
-  <si>
-    <t>24,92%</t>
-  </si>
-  <si>
-    <t>24,15%</t>
-  </si>
-  <si>
     <t>25,3%</t>
   </si>
   <si>
@@ -1134,6 +1134,18 @@
     <t>23,78%</t>
   </si>
   <si>
+    <t>51,25%</t>
+  </si>
+  <si>
+    <t>52,05%</t>
+  </si>
+  <si>
+    <t>50,63%</t>
+  </si>
+  <si>
+    <t>52,35%</t>
+  </si>
+  <si>
     <t>48,75%</t>
   </si>
   <si>
@@ -1146,21 +1158,24 @@
     <t>47,65%</t>
   </si>
   <si>
-    <t>51,25%</t>
-  </si>
-  <si>
-    <t>52,05%</t>
-  </si>
-  <si>
-    <t>50,63%</t>
-  </si>
-  <si>
-    <t>52,35%</t>
-  </si>
-  <si>
     <t>Córdoba</t>
   </si>
   <si>
+    <t>10,41%</t>
+  </si>
+  <si>
+    <t>9,5%</t>
+  </si>
+  <si>
+    <t>9,2%</t>
+  </si>
+  <si>
+    <t>10,34%</t>
+  </si>
+  <si>
+    <t>9,85%</t>
+  </si>
+  <si>
     <t>9,14%</t>
   </si>
   <si>
@@ -1176,21 +1191,6 @@
     <t>9,22%</t>
   </si>
   <si>
-    <t>10,41%</t>
-  </si>
-  <si>
-    <t>9,5%</t>
-  </si>
-  <si>
-    <t>9,2%</t>
-  </si>
-  <si>
-    <t>10,34%</t>
-  </si>
-  <si>
-    <t>9,85%</t>
-  </si>
-  <si>
     <t>9,79%</t>
   </si>
   <si>
@@ -1203,6 +1203,18 @@
     <t>9,54%</t>
   </si>
   <si>
+    <t>27,29%</t>
+  </si>
+  <si>
+    <t>24,64%</t>
+  </si>
+  <si>
+    <t>23,67%</t>
+  </si>
+  <si>
+    <t>24,4%</t>
+  </si>
+  <si>
     <t>24,93%</t>
   </si>
   <si>
@@ -1215,24 +1227,27 @@
     <t>26,01%</t>
   </si>
   <si>
-    <t>27,29%</t>
-  </si>
-  <si>
-    <t>24,64%</t>
-  </si>
-  <si>
-    <t>23,67%</t>
-  </si>
-  <si>
-    <t>24,4%</t>
-  </si>
-  <si>
     <t>26,18%</t>
   </si>
   <si>
     <t>23,76%</t>
   </si>
   <si>
+    <t>54,85%</t>
+  </si>
+  <si>
+    <t>52,04%</t>
+  </si>
+  <si>
+    <t>52,41%</t>
+  </si>
+  <si>
+    <t>51,01%</t>
+  </si>
+  <si>
+    <t>52,6%</t>
+  </si>
+  <si>
     <t>45,15%</t>
   </si>
   <si>
@@ -1248,24 +1263,24 @@
     <t>47,4%</t>
   </si>
   <si>
-    <t>54,85%</t>
-  </si>
-  <si>
-    <t>52,04%</t>
-  </si>
-  <si>
-    <t>52,41%</t>
-  </si>
-  <si>
-    <t>51,01%</t>
-  </si>
-  <si>
-    <t>52,6%</t>
-  </si>
-  <si>
     <t>Granada</t>
   </si>
   <si>
+    <t>10,68%</t>
+  </si>
+  <si>
+    <t>10,43%</t>
+  </si>
+  <si>
+    <t>10,05%</t>
+  </si>
+  <si>
+    <t>6,96%</t>
+  </si>
+  <si>
+    <t>9,59%</t>
+  </si>
+  <si>
     <t>11,2%</t>
   </si>
   <si>
@@ -1281,21 +1296,6 @@
     <t>10,72%</t>
   </si>
   <si>
-    <t>10,68%</t>
-  </si>
-  <si>
-    <t>10,43%</t>
-  </si>
-  <si>
-    <t>10,05%</t>
-  </si>
-  <si>
-    <t>6,96%</t>
-  </si>
-  <si>
-    <t>9,59%</t>
-  </si>
-  <si>
     <t>10,93%</t>
   </si>
   <si>
@@ -1311,21 +1311,21 @@
     <t>10,15%</t>
   </si>
   <si>
+    <t>28,78%</t>
+  </si>
+  <si>
+    <t>27,79%</t>
+  </si>
+  <si>
+    <t>26,55%</t>
+  </si>
+  <si>
+    <t>16,87%</t>
+  </si>
+  <si>
     <t>21,66%</t>
   </si>
   <si>
-    <t>28,78%</t>
-  </si>
-  <si>
-    <t>27,79%</t>
-  </si>
-  <si>
-    <t>26,55%</t>
-  </si>
-  <si>
-    <t>16,87%</t>
-  </si>
-  <si>
     <t>27,48%</t>
   </si>
   <si>
@@ -1338,6 +1338,18 @@
     <t>19,35%</t>
   </si>
   <si>
+    <t>50,43%</t>
+  </si>
+  <si>
+    <t>49,56%</t>
+  </si>
+  <si>
+    <t>41,98%</t>
+  </si>
+  <si>
+    <t>48,15%</t>
+  </si>
+  <si>
     <t>49,57%</t>
   </si>
   <si>
@@ -1350,21 +1362,21 @@
     <t>51,85%</t>
   </si>
   <si>
-    <t>50,43%</t>
-  </si>
-  <si>
-    <t>49,56%</t>
-  </si>
-  <si>
-    <t>41,98%</t>
-  </si>
-  <si>
-    <t>48,15%</t>
-  </si>
-  <si>
     <t>Huelva</t>
   </si>
   <si>
+    <t>5,89%</t>
+  </si>
+  <si>
+    <t>6,05%</t>
+  </si>
+  <si>
+    <t>6,38%</t>
+  </si>
+  <si>
+    <t>7,27%</t>
+  </si>
+  <si>
     <t>5,99%</t>
   </si>
   <si>
@@ -1380,18 +1392,6 @@
     <t>6,18%</t>
   </si>
   <si>
-    <t>5,89%</t>
-  </si>
-  <si>
-    <t>6,05%</t>
-  </si>
-  <si>
-    <t>6,38%</t>
-  </si>
-  <si>
-    <t>7,27%</t>
-  </si>
-  <si>
     <t>5,86%</t>
   </si>
   <si>
@@ -1404,21 +1404,33 @@
     <t>6,28%</t>
   </si>
   <si>
+    <t>23,88%</t>
+  </si>
+  <si>
+    <t>25,37%</t>
+  </si>
+  <si>
     <t>23,2%</t>
   </si>
   <si>
     <t>27,2%</t>
   </si>
   <si>
-    <t>23,88%</t>
-  </si>
-  <si>
-    <t>25,37%</t>
-  </si>
-  <si>
     <t>23,75%</t>
   </si>
   <si>
+    <t>51,2%</t>
+  </si>
+  <si>
+    <t>52,85%</t>
+  </si>
+  <si>
+    <t>51,91%</t>
+  </si>
+  <si>
+    <t>51,74%</t>
+  </si>
+  <si>
     <t>48,8%</t>
   </si>
   <si>
@@ -1431,21 +1443,24 @@
     <t>48,26%</t>
   </si>
   <si>
-    <t>51,2%</t>
-  </si>
-  <si>
-    <t>52,85%</t>
-  </si>
-  <si>
-    <t>51,91%</t>
-  </si>
-  <si>
-    <t>51,74%</t>
-  </si>
-  <si>
     <t>Jaén</t>
   </si>
   <si>
+    <t>8,66%</t>
+  </si>
+  <si>
+    <t>7,73%</t>
+  </si>
+  <si>
+    <t>7,14%</t>
+  </si>
+  <si>
+    <t>9,52%</t>
+  </si>
+  <si>
+    <t>8,23%</t>
+  </si>
+  <si>
     <t>8,06%</t>
   </si>
   <si>
@@ -1461,21 +1476,6 @@
     <t>7,88%</t>
   </si>
   <si>
-    <t>8,66%</t>
-  </si>
-  <si>
-    <t>7,73%</t>
-  </si>
-  <si>
-    <t>7,14%</t>
-  </si>
-  <si>
-    <t>9,52%</t>
-  </si>
-  <si>
-    <t>8,23%</t>
-  </si>
-  <si>
     <t>8,37%</t>
   </si>
   <si>
@@ -1488,30 +1488,42 @@
     <t>8,96%</t>
   </si>
   <si>
+    <t>27,17%</t>
+  </si>
+  <si>
+    <t>23,99%</t>
+  </si>
+  <si>
+    <t>21,97%</t>
+  </si>
+  <si>
+    <t>26,88%</t>
+  </si>
+  <si>
     <t>25,71%</t>
   </si>
   <si>
     <t>24,76%</t>
   </si>
   <si>
-    <t>27,17%</t>
-  </si>
-  <si>
-    <t>23,99%</t>
-  </si>
-  <si>
-    <t>21,97%</t>
-  </si>
-  <si>
-    <t>26,88%</t>
-  </si>
-  <si>
     <t>26,47%</t>
   </si>
   <si>
     <t>23,31%</t>
   </si>
   <si>
+    <t>51,23%</t>
+  </si>
+  <si>
+    <t>49,03%</t>
+  </si>
+  <si>
+    <t>54,07%</t>
+  </si>
+  <si>
+    <t>52,03%</t>
+  </si>
+  <si>
     <t>48,77%</t>
   </si>
   <si>
@@ -1524,21 +1536,21 @@
     <t>47,97%</t>
   </si>
   <si>
-    <t>51,23%</t>
-  </si>
-  <si>
-    <t>49,03%</t>
-  </si>
-  <si>
-    <t>54,07%</t>
-  </si>
-  <si>
-    <t>52,03%</t>
-  </si>
-  <si>
     <t>Málaga</t>
   </si>
   <si>
+    <t>18,14%</t>
+  </si>
+  <si>
+    <t>19,53%</t>
+  </si>
+  <si>
+    <t>18,22%</t>
+  </si>
+  <si>
+    <t>18,8%</t>
+  </si>
+  <si>
     <t>18,27%</t>
   </si>
   <si>
@@ -1551,18 +1563,6 @@
     <t>18,66%</t>
   </si>
   <si>
-    <t>18,14%</t>
-  </si>
-  <si>
-    <t>19,53%</t>
-  </si>
-  <si>
-    <t>18,22%</t>
-  </si>
-  <si>
-    <t>18,8%</t>
-  </si>
-  <si>
     <t>18,2%</t>
   </si>
   <si>
@@ -1590,6 +1590,18 @@
     <t>22,81%</t>
   </si>
   <si>
+    <t>51,44%</t>
+  </si>
+  <si>
+    <t>51,75%</t>
+  </si>
+  <si>
+    <t>50,12%</t>
+  </si>
+  <si>
+    <t>50,9%</t>
+  </si>
+  <si>
     <t>48,56%</t>
   </si>
   <si>
@@ -1602,21 +1614,21 @@
     <t>49,1%</t>
   </si>
   <si>
-    <t>51,44%</t>
-  </si>
-  <si>
-    <t>51,75%</t>
-  </si>
-  <si>
-    <t>50,12%</t>
-  </si>
-  <si>
-    <t>50,9%</t>
-  </si>
-  <si>
     <t>Sevilla</t>
   </si>
   <si>
+    <t>23,37%</t>
+  </si>
+  <si>
+    <t>23,94%</t>
+  </si>
+  <si>
+    <t>21,29%</t>
+  </si>
+  <si>
+    <t>23,01%</t>
+  </si>
+  <si>
     <t>24,6%</t>
   </si>
   <si>
@@ -1626,42 +1638,45 @@
     <t>23,23%</t>
   </si>
   <si>
-    <t>23,37%</t>
-  </si>
-  <si>
-    <t>23,94%</t>
-  </si>
-  <si>
-    <t>21,29%</t>
-  </si>
-  <si>
-    <t>23,01%</t>
-  </si>
-  <si>
     <t>24,27%</t>
   </si>
   <si>
     <t>23,12%</t>
   </si>
   <si>
+    <t>26,37%</t>
+  </si>
+  <si>
+    <t>21,51%</t>
+  </si>
+  <si>
     <t>27,77%</t>
   </si>
   <si>
     <t>20,32%</t>
   </si>
   <si>
-    <t>26,37%</t>
-  </si>
-  <si>
-    <t>21,51%</t>
-  </si>
-  <si>
     <t>25,9%</t>
   </si>
   <si>
     <t>20,92%</t>
   </si>
   <si>
+    <t>51,21%</t>
+  </si>
+  <si>
+    <t>50,4%</t>
+  </si>
+  <si>
+    <t>49,42%</t>
+  </si>
+  <si>
+    <t>52,13%</t>
+  </si>
+  <si>
+    <t>50,71%</t>
+  </si>
+  <si>
     <t>48,79%</t>
   </si>
   <si>
@@ -1677,24 +1692,21 @@
     <t>49,29%</t>
   </si>
   <si>
-    <t>51,21%</t>
-  </si>
-  <si>
-    <t>50,4%</t>
-  </si>
-  <si>
-    <t>49,42%</t>
-  </si>
-  <si>
-    <t>52,13%</t>
-  </si>
-  <si>
-    <t>50,71%</t>
-  </si>
-  <si>
     <t>Primarios</t>
   </si>
   <si>
+    <t>11,98%</t>
+  </si>
+  <si>
+    <t>11,28%</t>
+  </si>
+  <si>
+    <t>9,3%</t>
+  </si>
+  <si>
+    <t>8,5%</t>
+  </si>
+  <si>
     <t>13,36%</t>
   </si>
   <si>
@@ -1707,18 +1719,6 @@
     <t>10,58%</t>
   </si>
   <si>
-    <t>11,98%</t>
-  </si>
-  <si>
-    <t>11,28%</t>
-  </si>
-  <si>
-    <t>9,3%</t>
-  </si>
-  <si>
-    <t>8,5%</t>
-  </si>
-  <si>
     <t>12,65%</t>
   </si>
   <si>
@@ -1731,6 +1731,18 @@
     <t>7,92%</t>
   </si>
   <si>
+    <t>30,02%</t>
+  </si>
+  <si>
+    <t>27,94%</t>
+  </si>
+  <si>
+    <t>22,86%</t>
+  </si>
+  <si>
+    <t>19,17%</t>
+  </si>
+  <si>
     <t>31,78%</t>
   </si>
   <si>
@@ -1743,18 +1755,6 @@
     <t>16,12%</t>
   </si>
   <si>
-    <t>30,02%</t>
-  </si>
-  <si>
-    <t>27,94%</t>
-  </si>
-  <si>
-    <t>22,86%</t>
-  </si>
-  <si>
-    <t>19,17%</t>
-  </si>
-  <si>
     <t>30,89%</t>
   </si>
   <si>
@@ -1767,6 +1767,21 @@
     <t>17,65%</t>
   </si>
   <si>
+    <t>48,87%</t>
+  </si>
+  <si>
+    <t>47,45%</t>
+  </si>
+  <si>
+    <t>52,66%</t>
+  </si>
+  <si>
+    <t>54,61%</t>
+  </si>
+  <si>
+    <t>50,29%</t>
+  </si>
+  <si>
     <t>51,13%</t>
   </si>
   <si>
@@ -1782,24 +1797,24 @@
     <t>49,71%</t>
   </si>
   <si>
-    <t>48,87%</t>
-  </si>
-  <si>
-    <t>47,45%</t>
-  </si>
-  <si>
-    <t>52,66%</t>
-  </si>
-  <si>
-    <t>54,61%</t>
-  </si>
-  <si>
-    <t>50,29%</t>
-  </si>
-  <si>
     <t>Secundarios</t>
   </si>
   <si>
+    <t>66,27%</t>
+  </si>
+  <si>
+    <t>65,98%</t>
+  </si>
+  <si>
+    <t>65,26%</t>
+  </si>
+  <si>
+    <t>67,14%</t>
+  </si>
+  <si>
+    <t>66,14%</t>
+  </si>
+  <si>
     <t>61,69%</t>
   </si>
   <si>
@@ -1815,21 +1830,6 @@
     <t>65,25%</t>
   </si>
   <si>
-    <t>66,27%</t>
-  </si>
-  <si>
-    <t>65,98%</t>
-  </si>
-  <si>
-    <t>65,26%</t>
-  </si>
-  <si>
-    <t>67,14%</t>
-  </si>
-  <si>
-    <t>66,14%</t>
-  </si>
-  <si>
     <t>64,05%</t>
   </si>
   <si>
@@ -1842,24 +1842,39 @@
     <t>65,7%</t>
   </si>
   <si>
+    <t>25,88%</t>
+  </si>
+  <si>
+    <t>25,49%</t>
+  </si>
+  <si>
+    <t>25,02%</t>
+  </si>
+  <si>
     <t>23,79%</t>
   </si>
   <si>
-    <t>25,88%</t>
-  </si>
-  <si>
-    <t>25,49%</t>
-  </si>
-  <si>
-    <t>25,02%</t>
-  </si>
-  <si>
     <t>24,86%</t>
   </si>
   <si>
     <t>23,98%</t>
   </si>
   <si>
+    <t>53,38%</t>
+  </si>
+  <si>
+    <t>51,94%</t>
+  </si>
+  <si>
+    <t>49,33%</t>
+  </si>
+  <si>
+    <t>50,5%</t>
+  </si>
+  <si>
+    <t>51,27%</t>
+  </si>
+  <si>
     <t>46,62%</t>
   </si>
   <si>
@@ -1875,24 +1890,15 @@
     <t>48,73%</t>
   </si>
   <si>
-    <t>53,38%</t>
-  </si>
-  <si>
-    <t>51,94%</t>
-  </si>
-  <si>
-    <t>49,33%</t>
-  </si>
-  <si>
-    <t>50,5%</t>
-  </si>
-  <si>
-    <t>51,27%</t>
-  </si>
-  <si>
     <t>Universitarios</t>
   </si>
   <si>
+    <t>22,74%</t>
+  </si>
+  <si>
+    <t>23,55%</t>
+  </si>
+  <si>
     <t>24,95%</t>
   </si>
   <si>
@@ -1905,36 +1911,39 @@
     <t>24,42%</t>
   </si>
   <si>
-    <t>22,74%</t>
-  </si>
-  <si>
-    <t>23,55%</t>
-  </si>
-  <si>
     <t>22,88%</t>
   </si>
   <si>
     <t>24,88%</t>
   </si>
   <si>
+    <t>27,4%</t>
+  </si>
+  <si>
+    <t>24,06%</t>
+  </si>
+  <si>
     <t>26,38%</t>
   </si>
   <si>
     <t>23,52%</t>
   </si>
   <si>
-    <t>27,4%</t>
-  </si>
-  <si>
-    <t>24,06%</t>
-  </si>
-  <si>
     <t>24,91%</t>
   </si>
   <si>
     <t>26,89%</t>
   </si>
   <si>
+    <t>48,16%</t>
+  </si>
+  <si>
+    <t>50,83%</t>
+  </si>
+  <si>
+    <t>50,85%</t>
+  </si>
+  <si>
     <t>51,84%</t>
   </si>
   <si>
@@ -1944,15 +1953,6 @@
     <t>49,15%</t>
   </si>
   <si>
-    <t>48,16%</t>
-  </si>
-  <si>
-    <t>50,83%</t>
-  </si>
-  <si>
-    <t>50,85%</t>
-  </si>
-  <si>
     <t>25,83%</t>
   </si>
   <si>
@@ -1971,6 +1971,15 @@
     <t>23,27%</t>
   </si>
   <si>
+    <t>51,59%</t>
+  </si>
+  <si>
+    <t>50,91%</t>
+  </si>
+  <si>
+    <t>50,93%</t>
+  </si>
+  <si>
     <t>48,41%</t>
   </si>
   <si>
@@ -1980,18 +1989,24 @@
     <t>49,07%</t>
   </si>
   <si>
-    <t>51,59%</t>
-  </si>
-  <si>
-    <t>50,91%</t>
-  </si>
-  <si>
-    <t>50,93%</t>
-  </si>
-  <si>
     <t>Grupo I y II</t>
   </si>
   <si>
+    <t>14,19%</t>
+  </si>
+  <si>
+    <t>12,71%</t>
+  </si>
+  <si>
+    <t>14,26%</t>
+  </si>
+  <si>
+    <t>17,83%</t>
+  </si>
+  <si>
+    <t>14,7%</t>
+  </si>
+  <si>
     <t>16,05%</t>
   </si>
   <si>
@@ -2007,21 +2022,6 @@
     <t>14,6%</t>
   </si>
   <si>
-    <t>14,19%</t>
-  </si>
-  <si>
-    <t>12,71%</t>
-  </si>
-  <si>
-    <t>14,26%</t>
-  </si>
-  <si>
-    <t>17,83%</t>
-  </si>
-  <si>
-    <t>14,7%</t>
-  </si>
-  <si>
     <t>15,09%</t>
   </si>
   <si>
@@ -2037,6 +2037,18 @@
     <t>14,65%</t>
   </si>
   <si>
+    <t>24,66%</t>
+  </si>
+  <si>
+    <t>21,96%</t>
+  </si>
+  <si>
+    <t>24,49%</t>
+  </si>
+  <si>
+    <t>28,89%</t>
+  </si>
+  <si>
     <t>27,03%</t>
   </si>
   <si>
@@ -2049,18 +2061,6 @@
     <t>27,74%</t>
   </si>
   <si>
-    <t>24,66%</t>
-  </si>
-  <si>
-    <t>21,96%</t>
-  </si>
-  <si>
-    <t>24,49%</t>
-  </si>
-  <si>
-    <t>28,89%</t>
-  </si>
-  <si>
     <t>25,82%</t>
   </si>
   <si>
@@ -2073,21 +2073,36 @@
     <t>28,32%</t>
   </si>
   <si>
+    <t>53,51%</t>
+  </si>
+  <si>
+    <t>51,12%</t>
+  </si>
+  <si>
     <t>46,49%</t>
   </si>
   <si>
     <t>48,88%</t>
   </si>
   <si>
-    <t>53,51%</t>
-  </si>
-  <si>
-    <t>51,12%</t>
-  </si>
-  <si>
     <t>Grupo III</t>
   </si>
   <si>
+    <t>12,63%</t>
+  </si>
+  <si>
+    <t>13,69%</t>
+  </si>
+  <si>
+    <t>16,22%</t>
+  </si>
+  <si>
+    <t>13,66%</t>
+  </si>
+  <si>
+    <t>14,05%</t>
+  </si>
+  <si>
     <t>13,64%</t>
   </si>
   <si>
@@ -2103,21 +2118,6 @@
     <t>14,53%</t>
   </si>
   <si>
-    <t>12,63%</t>
-  </si>
-  <si>
-    <t>13,69%</t>
-  </si>
-  <si>
-    <t>16,22%</t>
-  </si>
-  <si>
-    <t>13,66%</t>
-  </si>
-  <si>
-    <t>14,05%</t>
-  </si>
-  <si>
     <t>13,12%</t>
   </si>
   <si>
@@ -2133,6 +2133,15 @@
     <t>14,28%</t>
   </si>
   <si>
+    <t>24,73%</t>
+  </si>
+  <si>
+    <t>29,15%</t>
+  </si>
+  <si>
+    <t>23,14%</t>
+  </si>
+  <si>
     <t>23,09%</t>
   </si>
   <si>
@@ -2142,15 +2151,6 @@
     <t>27,71%</t>
   </si>
   <si>
-    <t>24,73%</t>
-  </si>
-  <si>
-    <t>29,15%</t>
-  </si>
-  <si>
-    <t>23,14%</t>
-  </si>
-  <si>
     <t>24,45%</t>
   </si>
   <si>
@@ -2160,21 +2160,33 @@
     <t>24,09%</t>
   </si>
   <si>
+    <t>51,4%</t>
+  </si>
+  <si>
+    <t>50,13%</t>
+  </si>
+  <si>
     <t>48,6%</t>
   </si>
   <si>
     <t>49,87%</t>
   </si>
   <si>
-    <t>51,4%</t>
-  </si>
-  <si>
-    <t>50,13%</t>
-  </si>
-  <si>
     <t>Grupo IV y V</t>
   </si>
   <si>
+    <t>14,38%</t>
+  </si>
+  <si>
+    <t>12,22%</t>
+  </si>
+  <si>
+    <t>10,91%</t>
+  </si>
+  <si>
+    <t>11,62%</t>
+  </si>
+  <si>
     <t>10,6%</t>
   </si>
   <si>
@@ -2187,18 +2199,6 @@
     <t>10,24%</t>
   </si>
   <si>
-    <t>14,38%</t>
-  </si>
-  <si>
-    <t>12,22%</t>
-  </si>
-  <si>
-    <t>10,91%</t>
-  </si>
-  <si>
-    <t>11,62%</t>
-  </si>
-  <si>
     <t>12,56%</t>
   </si>
   <si>
@@ -2211,21 +2211,21 @@
     <t>10,94%</t>
   </si>
   <si>
+    <t>31,62%</t>
+  </si>
+  <si>
+    <t>26,71%</t>
+  </si>
+  <si>
+    <t>17,95%</t>
+  </si>
+  <si>
     <t>31,74%</t>
   </si>
   <si>
     <t>18,89%</t>
   </si>
   <si>
-    <t>31,62%</t>
-  </si>
-  <si>
-    <t>26,71%</t>
-  </si>
-  <si>
-    <t>17,95%</t>
-  </si>
-  <si>
     <t>28,79%</t>
   </si>
   <si>
@@ -2238,6 +2238,18 @@
     <t>18,38%</t>
   </si>
   <si>
+    <t>59,44%</t>
+  </si>
+  <si>
+    <t>53,88%</t>
+  </si>
+  <si>
+    <t>52,83%</t>
+  </si>
+  <si>
+    <t>54,1%</t>
+  </si>
+  <si>
     <t>40,56%</t>
   </si>
   <si>
@@ -2250,21 +2262,24 @@
     <t>45,9%</t>
   </si>
   <si>
-    <t>59,44%</t>
-  </si>
-  <si>
-    <t>53,88%</t>
-  </si>
-  <si>
-    <t>52,83%</t>
-  </si>
-  <si>
-    <t>54,1%</t>
-  </si>
-  <si>
     <t>Grupo VI</t>
   </si>
   <si>
+    <t>29,54%</t>
+  </si>
+  <si>
+    <t>31,67%</t>
+  </si>
+  <si>
+    <t>29,6%</t>
+  </si>
+  <si>
+    <t>29,72%</t>
+  </si>
+  <si>
+    <t>30,14%</t>
+  </si>
+  <si>
     <t>31,79%</t>
   </si>
   <si>
@@ -2280,21 +2295,6 @@
     <t>31,5%</t>
   </si>
   <si>
-    <t>29,54%</t>
-  </si>
-  <si>
-    <t>31,67%</t>
-  </si>
-  <si>
-    <t>29,6%</t>
-  </si>
-  <si>
-    <t>29,72%</t>
-  </si>
-  <si>
-    <t>30,14%</t>
-  </si>
-  <si>
     <t>31,1%</t>
   </si>
   <si>
@@ -2307,6 +2307,12 @@
     <t>30,81%</t>
   </si>
   <si>
+    <t>26,69%</t>
+  </si>
+  <si>
+    <t>24,79%</t>
+  </si>
+  <si>
     <t>24,82%</t>
   </si>
   <si>
@@ -2316,15 +2322,21 @@
     <t>22,77%</t>
   </si>
   <si>
-    <t>26,69%</t>
-  </si>
-  <si>
-    <t>24,79%</t>
-  </si>
-  <si>
     <t>25,59%</t>
   </si>
   <si>
+    <t>50,08%</t>
+  </si>
+  <si>
+    <t>46,88%</t>
+  </si>
+  <si>
+    <t>50,62%</t>
+  </si>
+  <si>
+    <t>49,86%</t>
+  </si>
+  <si>
     <t>49,92%</t>
   </si>
   <si>
@@ -2337,21 +2349,21 @@
     <t>50,14%</t>
   </si>
   <si>
-    <t>50,08%</t>
-  </si>
-  <si>
-    <t>46,88%</t>
-  </si>
-  <si>
-    <t>50,62%</t>
-  </si>
-  <si>
-    <t>49,86%</t>
-  </si>
-  <si>
     <t>Grupo VII</t>
   </si>
   <si>
+    <t>19,26%</t>
+  </si>
+  <si>
+    <t>19,47%</t>
+  </si>
+  <si>
+    <t>20,65%</t>
+  </si>
+  <si>
+    <t>19,49%</t>
+  </si>
+  <si>
     <t>16,37%</t>
   </si>
   <si>
@@ -2364,18 +2376,6 @@
     <t>19,48%</t>
   </si>
   <si>
-    <t>19,26%</t>
-  </si>
-  <si>
-    <t>19,47%</t>
-  </si>
-  <si>
-    <t>20,65%</t>
-  </si>
-  <si>
-    <t>19,49%</t>
-  </si>
-  <si>
     <t>20,47%</t>
   </si>
   <si>
@@ -2385,6 +2385,15 @@
     <t>20,01%</t>
   </si>
   <si>
+    <t>24,46%</t>
+  </si>
+  <si>
+    <t>25,1%</t>
+  </si>
+  <si>
+    <t>25,22%</t>
+  </si>
+  <si>
     <t>20,66%</t>
   </si>
   <si>
@@ -2394,15 +2403,6 @@
     <t>27,28%</t>
   </si>
   <si>
-    <t>24,46%</t>
-  </si>
-  <si>
-    <t>25,1%</t>
-  </si>
-  <si>
-    <t>25,22%</t>
-  </si>
-  <si>
     <t>22,6%</t>
   </si>
   <si>
@@ -2415,6 +2415,15 @@
     <t>24,55%</t>
   </si>
   <si>
+    <t>55,17%</t>
+  </si>
+  <si>
+    <t>48,05%</t>
+  </si>
+  <si>
+    <t>49,01%</t>
+  </si>
+  <si>
     <t>44,83%</t>
   </si>
   <si>
@@ -2424,18 +2433,18 @@
     <t>50,99%</t>
   </si>
   <si>
-    <t>55,17%</t>
-  </si>
-  <si>
-    <t>48,05%</t>
-  </si>
-  <si>
-    <t>49,01%</t>
-  </si>
-  <si>
     <t>No ha trabajado</t>
   </si>
   <si>
+    <t>10,59%</t>
+  </si>
+  <si>
+    <t>10,46%</t>
+  </si>
+  <si>
+    <t>10,0%</t>
+  </si>
+  <si>
     <t>11,54%</t>
   </si>
   <si>
@@ -2451,15 +2460,6 @@
     <t>9,65%</t>
   </si>
   <si>
-    <t>10,59%</t>
-  </si>
-  <si>
-    <t>10,46%</t>
-  </si>
-  <si>
-    <t>10,0%</t>
-  </si>
-  <si>
     <t>11,05%</t>
   </si>
   <si>
@@ -2472,18 +2472,30 @@
     <t>9,83%</t>
   </si>
   <si>
+    <t>22,33%</t>
+  </si>
+  <si>
     <t>29,41%</t>
   </si>
   <si>
     <t>23,8%</t>
   </si>
   <si>
-    <t>22,33%</t>
-  </si>
-  <si>
     <t>28,19%</t>
   </si>
   <si>
+    <t>49,77%</t>
+  </si>
+  <si>
+    <t>58,47%</t>
+  </si>
+  <si>
+    <t>52,15%</t>
+  </si>
+  <si>
+    <t>51,87%</t>
+  </si>
+  <si>
     <t>50,23%</t>
   </si>
   <si>
@@ -2496,16 +2508,13 @@
     <t>48,13%</t>
   </si>
   <si>
-    <t>49,77%</t>
-  </si>
-  <si>
-    <t>58,47%</t>
-  </si>
-  <si>
-    <t>52,15%</t>
-  </si>
-  <si>
-    <t>51,87%</t>
+    <t>25,4%</t>
+  </si>
+  <si>
+    <t>25,25%</t>
+  </si>
+  <si>
+    <t>23,81%</t>
   </si>
   <si>
     <t>24,59%</t>
@@ -2517,15 +2526,6 @@
     <t>26,14%</t>
   </si>
   <si>
-    <t>25,4%</t>
-  </si>
-  <si>
-    <t>25,25%</t>
-  </si>
-  <si>
-    <t>23,81%</t>
-  </si>
-  <si>
     <t>25,08%</t>
   </si>
   <si>
@@ -2535,16 +2535,16 @@
     <t>23,9%</t>
   </si>
   <si>
+    <t>51,92%</t>
+  </si>
+  <si>
+    <t>50,96%</t>
+  </si>
+  <si>
     <t>48,08%</t>
   </si>
   <si>
     <t>49,04%</t>
-  </si>
-  <si>
-    <t>51,92%</t>
-  </si>
-  <si>
-    <t>50,96%</t>
   </si>
   <si>
     <t>* Las casillas con valores enteros representan el número de entrevistas realizadas, es decir, personas que contestaron en cada edición; mientras que las casillas con porcentajes representan la distribución de las entrevistas realizadas en cada edición (% columna), en cada categoría de la variable de segmentación (% fila) o según sexo (% edición).</t>
@@ -2678,7 +2678,7 @@
         <xdr:cNvPr id="2" name="Gráfico 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52574BB1-4AE6-4B53-9D73-C72C85E5BE91}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2815363-912F-4D68-BFDA-DC492B66EED0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3110,34 +3110,34 @@
         <v>9</v>
       </c>
       <c r="C4" s="1">
+        <v>182</v>
+      </c>
+      <c r="D4" s="1">
+        <v>207</v>
+      </c>
+      <c r="E4" s="1">
+        <v>187</v>
+      </c>
+      <c r="F4" s="1">
+        <v>116</v>
+      </c>
+      <c r="G4" s="1">
+        <v>692</v>
+      </c>
+      <c r="H4" s="1">
         <v>162</v>
       </c>
-      <c r="D4" s="1">
+      <c r="I4" s="1">
         <v>219</v>
       </c>
-      <c r="E4" s="1">
+      <c r="J4" s="1">
         <v>211</v>
       </c>
-      <c r="F4" s="1">
+      <c r="K4" s="1">
         <v>109</v>
       </c>
-      <c r="G4" s="1">
+      <c r="L4" s="1">
         <v>701</v>
-      </c>
-      <c r="H4" s="1">
-        <v>182</v>
-      </c>
-      <c r="I4" s="1">
-        <v>207</v>
-      </c>
-      <c r="J4" s="1">
-        <v>187</v>
-      </c>
-      <c r="K4" s="1">
-        <v>116</v>
-      </c>
-      <c r="L4" s="1">
-        <v>692</v>
       </c>
       <c r="M4" s="1">
         <v>344</v>
@@ -3221,25 +3221,25 @@
         <v>29</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="G6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="L6" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>35</v>
@@ -3254,7 +3254,7 @@
         <v>38</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
@@ -3293,19 +3293,19 @@
         <v>49</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
@@ -3316,34 +3316,34 @@
         <v>9</v>
       </c>
       <c r="C8" s="1">
+        <v>382</v>
+      </c>
+      <c r="D8" s="1">
+        <v>374</v>
+      </c>
+      <c r="E8" s="1">
+        <v>380</v>
+      </c>
+      <c r="F8" s="1">
+        <v>276</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1412</v>
+      </c>
+      <c r="H8" s="1">
         <v>379</v>
       </c>
-      <c r="D8" s="1">
+      <c r="I8" s="1">
         <v>340</v>
       </c>
-      <c r="E8" s="1">
+      <c r="J8" s="1">
         <v>332</v>
       </c>
-      <c r="F8" s="1">
+      <c r="K8" s="1">
         <v>258</v>
       </c>
-      <c r="G8" s="1">
+      <c r="L8" s="1">
         <v>1309</v>
-      </c>
-      <c r="H8" s="1">
-        <v>382</v>
-      </c>
-      <c r="I8" s="1">
-        <v>374</v>
-      </c>
-      <c r="J8" s="1">
-        <v>380</v>
-      </c>
-      <c r="K8" s="1">
-        <v>276</v>
-      </c>
-      <c r="L8" s="1">
-        <v>1412</v>
       </c>
       <c r="M8" s="1">
         <v>761</v>
@@ -3430,7 +3430,7 @@
         <v>69</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>70</v>
@@ -3445,7 +3445,7 @@
         <v>73</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>74</v>
@@ -3460,7 +3460,7 @@
         <v>77</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
@@ -3499,19 +3499,19 @@
         <v>87</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
@@ -3522,34 +3522,34 @@
         <v>9</v>
       </c>
       <c r="C12" s="1">
+        <v>212</v>
+      </c>
+      <c r="D12" s="1">
+        <v>228</v>
+      </c>
+      <c r="E12" s="1">
+        <v>263</v>
+      </c>
+      <c r="F12" s="1">
+        <v>243</v>
+      </c>
+      <c r="G12" s="1">
+        <v>946</v>
+      </c>
+      <c r="H12" s="1">
         <v>191</v>
       </c>
-      <c r="D12" s="1">
+      <c r="I12" s="1">
         <v>223</v>
       </c>
-      <c r="E12" s="1">
+      <c r="J12" s="1">
         <v>272</v>
       </c>
-      <c r="F12" s="1">
+      <c r="K12" s="1">
         <v>234</v>
       </c>
-      <c r="G12" s="1">
+      <c r="L12" s="1">
         <v>920</v>
-      </c>
-      <c r="H12" s="1">
-        <v>212</v>
-      </c>
-      <c r="I12" s="1">
-        <v>228</v>
-      </c>
-      <c r="J12" s="1">
-        <v>263</v>
-      </c>
-      <c r="K12" s="1">
-        <v>243</v>
-      </c>
-      <c r="L12" s="1">
-        <v>946</v>
       </c>
       <c r="M12" s="1">
         <v>403</v>
@@ -3579,22 +3579,22 @@
         <v>90</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="J13" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>96</v>
@@ -3636,7 +3636,7 @@
         <v>106</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>107</v>
@@ -3651,7 +3651,7 @@
         <v>110</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>111</v>
@@ -3666,7 +3666,7 @@
         <v>114</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
@@ -3705,19 +3705,19 @@
         <v>124</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
@@ -3728,34 +3728,34 @@
         <v>9</v>
       </c>
       <c r="C16" s="1">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="D16" s="1">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="E16" s="1">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="F16" s="1">
         <v>342</v>
       </c>
       <c r="G16" s="1">
-        <v>1117</v>
+        <v>1152</v>
       </c>
       <c r="H16" s="1">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="I16" s="1">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="J16" s="1">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="K16" s="1">
         <v>342</v>
       </c>
       <c r="L16" s="1">
-        <v>1152</v>
+        <v>1117</v>
       </c>
       <c r="M16" s="1">
         <v>596</v>
@@ -3830,22 +3830,22 @@
         <v>26</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="G18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>144</v>
@@ -3857,7 +3857,7 @@
         <v>146</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>147</v>
@@ -3872,7 +3872,7 @@
         <v>150</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
@@ -3911,19 +3911,19 @@
         <v>159</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
@@ -3934,34 +3934,34 @@
         <v>9</v>
       </c>
       <c r="C20" s="1">
+        <v>1086</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1074</v>
+      </c>
+      <c r="E20" s="1">
+        <v>1065</v>
+      </c>
+      <c r="F20" s="1">
+        <v>977</v>
+      </c>
+      <c r="G20" s="1">
+        <v>4202</v>
+      </c>
+      <c r="H20" s="1">
         <v>1018</v>
       </c>
-      <c r="D20" s="1">
+      <c r="I20" s="1">
         <v>1025</v>
       </c>
-      <c r="E20" s="1">
+      <c r="J20" s="1">
         <v>1061</v>
       </c>
-      <c r="F20" s="1">
+      <c r="K20" s="1">
         <v>943</v>
       </c>
-      <c r="G20" s="1">
+      <c r="L20" s="1">
         <v>4047</v>
-      </c>
-      <c r="H20" s="1">
-        <v>1086</v>
-      </c>
-      <c r="I20" s="1">
-        <v>1074</v>
-      </c>
-      <c r="J20" s="1">
-        <v>1065</v>
-      </c>
-      <c r="K20" s="1">
-        <v>977</v>
-      </c>
-      <c r="L20" s="1">
-        <v>4202</v>
       </c>
       <c r="M20" s="1">
         <v>2104</v>
@@ -3985,49 +3985,49 @@
         <v>10</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
@@ -4039,22 +4039,22 @@
         <v>160</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="G22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H22" s="1" t="s">
+      <c r="I22" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>165</v>
@@ -4063,7 +4063,7 @@
         <v>166</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>167</v>
@@ -4078,7 +4078,7 @@
         <v>170</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
@@ -4117,19 +4117,19 @@
         <v>123</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
@@ -4342,34 +4342,34 @@
         <v>9</v>
       </c>
       <c r="C4" s="1">
+        <v>226</v>
+      </c>
+      <c r="D4" s="1">
+        <v>211</v>
+      </c>
+      <c r="E4" s="1">
+        <v>195</v>
+      </c>
+      <c r="F4" s="1">
+        <v>171</v>
+      </c>
+      <c r="G4" s="1">
+        <v>803</v>
+      </c>
+      <c r="H4" s="1">
         <v>203</v>
       </c>
-      <c r="D4" s="1">
+      <c r="I4" s="1">
         <v>189</v>
       </c>
-      <c r="E4" s="1">
+      <c r="J4" s="1">
         <v>187</v>
       </c>
-      <c r="F4" s="1">
+      <c r="K4" s="1">
         <v>196</v>
       </c>
-      <c r="G4" s="1">
+      <c r="L4" s="1">
         <v>775</v>
-      </c>
-      <c r="H4" s="1">
-        <v>226</v>
-      </c>
-      <c r="I4" s="1">
-        <v>211</v>
-      </c>
-      <c r="J4" s="1">
-        <v>195</v>
-      </c>
-      <c r="K4" s="1">
-        <v>171</v>
-      </c>
-      <c r="L4" s="1">
-        <v>803</v>
       </c>
       <c r="M4" s="1">
         <v>429</v>
@@ -4405,22 +4405,22 @@
         <v>184</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>190</v>
@@ -4432,7 +4432,7 @@
         <v>192</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="Q5" s="1" t="s">
         <v>193</v>
@@ -4456,7 +4456,7 @@
         <v>197</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>198</v>
@@ -4471,13 +4471,13 @@
         <v>201</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>202</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="O6" s="1" t="s">
         <v>203</v>
@@ -4486,7 +4486,7 @@
         <v>204</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
@@ -4525,19 +4525,19 @@
         <v>178</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
@@ -4548,34 +4548,34 @@
         <v>9</v>
       </c>
       <c r="C8" s="1">
+        <v>322</v>
+      </c>
+      <c r="D8" s="1">
+        <v>324</v>
+      </c>
+      <c r="E8" s="1">
+        <v>332</v>
+      </c>
+      <c r="F8" s="1">
+        <v>343</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1321</v>
+      </c>
+      <c r="H8" s="1">
         <v>312</v>
       </c>
-      <c r="D8" s="1">
+      <c r="I8" s="1">
         <v>319</v>
       </c>
-      <c r="E8" s="1">
+      <c r="J8" s="1">
         <v>334</v>
       </c>
-      <c r="F8" s="1">
+      <c r="K8" s="1">
         <v>280</v>
       </c>
-      <c r="G8" s="1">
+      <c r="L8" s="1">
         <v>1245</v>
-      </c>
-      <c r="H8" s="1">
-        <v>322</v>
-      </c>
-      <c r="I8" s="1">
-        <v>324</v>
-      </c>
-      <c r="J8" s="1">
-        <v>332</v>
-      </c>
-      <c r="K8" s="1">
-        <v>343</v>
-      </c>
-      <c r="L8" s="1">
-        <v>1321</v>
       </c>
       <c r="M8" s="1">
         <v>634</v>
@@ -4608,22 +4608,22 @@
         <v>216</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>146</v>
+        <v>217</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>221</v>
+        <v>142</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>222</v>
@@ -4659,40 +4659,40 @@
         <v>230</v>
       </c>
       <c r="F10" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="K10" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="L10" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>235</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>236</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
@@ -4731,19 +4731,19 @@
         <v>246</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
@@ -4754,34 +4754,34 @@
         <v>9</v>
       </c>
       <c r="C12" s="1">
+        <v>232</v>
+      </c>
+      <c r="D12" s="1">
+        <v>256</v>
+      </c>
+      <c r="E12" s="1">
+        <v>248</v>
+      </c>
+      <c r="F12" s="1">
+        <v>225</v>
+      </c>
+      <c r="G12" s="1">
+        <v>961</v>
+      </c>
+      <c r="H12" s="1">
         <v>229</v>
       </c>
-      <c r="D12" s="1">
+      <c r="I12" s="1">
         <v>242</v>
       </c>
-      <c r="E12" s="1">
+      <c r="J12" s="1">
         <v>259</v>
       </c>
-      <c r="F12" s="1">
+      <c r="K12" s="1">
         <v>227</v>
       </c>
-      <c r="G12" s="1">
+      <c r="L12" s="1">
         <v>957</v>
-      </c>
-      <c r="H12" s="1">
-        <v>232</v>
-      </c>
-      <c r="I12" s="1">
-        <v>256</v>
-      </c>
-      <c r="J12" s="1">
-        <v>248</v>
-      </c>
-      <c r="K12" s="1">
-        <v>225</v>
-      </c>
-      <c r="L12" s="1">
-        <v>961</v>
       </c>
       <c r="M12" s="1">
         <v>461</v>
@@ -4847,7 +4847,7 @@
         <v>261</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
@@ -4859,22 +4859,22 @@
         <v>262</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>197</v>
+        <v>263</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>266</v>
+        <v>201</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>267</v>
@@ -4883,7 +4883,7 @@
         <v>268</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>269</v>
@@ -4898,7 +4898,7 @@
         <v>272</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
@@ -4937,19 +4937,19 @@
         <v>280</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
@@ -4960,34 +4960,34 @@
         <v>9</v>
       </c>
       <c r="C16" s="1">
+        <v>306</v>
+      </c>
+      <c r="D16" s="1">
+        <v>283</v>
+      </c>
+      <c r="E16" s="1">
+        <v>290</v>
+      </c>
+      <c r="F16" s="1">
+        <v>238</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1117</v>
+      </c>
+      <c r="H16" s="1">
         <v>274</v>
       </c>
-      <c r="D16" s="1">
+      <c r="I16" s="1">
         <v>275</v>
       </c>
-      <c r="E16" s="1">
+      <c r="J16" s="1">
         <v>281</v>
       </c>
-      <c r="F16" s="1">
+      <c r="K16" s="1">
         <v>240</v>
       </c>
-      <c r="G16" s="1">
+      <c r="L16" s="1">
         <v>1070</v>
-      </c>
-      <c r="H16" s="1">
-        <v>306</v>
-      </c>
-      <c r="I16" s="1">
-        <v>283</v>
-      </c>
-      <c r="J16" s="1">
-        <v>290</v>
-      </c>
-      <c r="K16" s="1">
-        <v>238</v>
-      </c>
-      <c r="L16" s="1">
-        <v>1117</v>
       </c>
       <c r="M16" s="1">
         <v>580</v>
@@ -5014,28 +5014,28 @@
         <v>282</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>230</v>
+        <v>283</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F17" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>288</v>
       </c>
       <c r="L17" s="1" t="s">
         <v>289</v>
@@ -5044,7 +5044,7 @@
         <v>290</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="O17" s="1" t="s">
         <v>291</v>
@@ -5068,28 +5068,28 @@
         <v>295</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="G18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H18" s="1" t="s">
+      <c r="I18" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="J18" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>270</v>
       </c>
       <c r="K18" s="1" t="s">
         <v>300</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>301</v>
@@ -5104,7 +5104,7 @@
         <v>303</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
@@ -5143,19 +5143,19 @@
         <v>311</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
@@ -5166,34 +5166,34 @@
         <v>9</v>
       </c>
       <c r="C20" s="1">
+        <v>1086</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1074</v>
+      </c>
+      <c r="E20" s="1">
+        <v>1065</v>
+      </c>
+      <c r="F20" s="1">
+        <v>977</v>
+      </c>
+      <c r="G20" s="1">
+        <v>4202</v>
+      </c>
+      <c r="H20" s="1">
         <v>1018</v>
       </c>
-      <c r="D20" s="1">
+      <c r="I20" s="1">
         <v>1025</v>
       </c>
-      <c r="E20" s="1">
+      <c r="J20" s="1">
         <v>1061</v>
       </c>
-      <c r="F20" s="1">
+      <c r="K20" s="1">
         <v>943</v>
       </c>
-      <c r="G20" s="1">
+      <c r="L20" s="1">
         <v>4047</v>
-      </c>
-      <c r="H20" s="1">
-        <v>1086</v>
-      </c>
-      <c r="I20" s="1">
-        <v>1074</v>
-      </c>
-      <c r="J20" s="1">
-        <v>1065</v>
-      </c>
-      <c r="K20" s="1">
-        <v>977</v>
-      </c>
-      <c r="L20" s="1">
-        <v>4202</v>
       </c>
       <c r="M20" s="1">
         <v>2104</v>
@@ -5217,49 +5217,49 @@
         <v>10</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
@@ -5271,22 +5271,22 @@
         <v>160</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="G22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H22" s="1" t="s">
+      <c r="I22" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>165</v>
@@ -5295,7 +5295,7 @@
         <v>166</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>167</v>
@@ -5310,7 +5310,7 @@
         <v>170</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
@@ -5349,19 +5349,19 @@
         <v>123</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
@@ -5577,31 +5577,31 @@
         <v>85</v>
       </c>
       <c r="D4" s="1">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E4" s="1">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F4" s="1">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G4" s="1">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="H4" s="1">
         <v>85</v>
       </c>
       <c r="I4" s="1">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J4" s="1">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K4" s="1">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="L4" s="1">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="M4" s="1">
         <v>170</v>
@@ -5682,43 +5682,43 @@
         <v>329</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>110</v>
+        <v>330</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>333</v>
-      </c>
       <c r="L6" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>334</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>335</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
@@ -5757,19 +5757,19 @@
         <v>343</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
@@ -5780,34 +5780,34 @@
         <v>9</v>
       </c>
       <c r="C8" s="1">
+        <v>164</v>
+      </c>
+      <c r="D8" s="1">
+        <v>165</v>
+      </c>
+      <c r="E8" s="1">
+        <v>161</v>
+      </c>
+      <c r="F8" s="1">
         <v>156</v>
       </c>
-      <c r="D8" s="1">
+      <c r="G8" s="1">
+        <v>646</v>
+      </c>
+      <c r="H8" s="1">
+        <v>156</v>
+      </c>
+      <c r="I8" s="1">
         <v>152</v>
       </c>
-      <c r="E8" s="1">
+      <c r="J8" s="1">
         <v>157</v>
       </c>
-      <c r="F8" s="1">
+      <c r="K8" s="1">
         <v>142</v>
       </c>
-      <c r="G8" s="1">
+      <c r="L8" s="1">
         <v>607</v>
-      </c>
-      <c r="H8" s="1">
-        <v>164</v>
-      </c>
-      <c r="I8" s="1">
-        <v>165</v>
-      </c>
-      <c r="J8" s="1">
-        <v>161</v>
-      </c>
-      <c r="K8" s="1">
-        <v>156</v>
-      </c>
-      <c r="L8" s="1">
-        <v>646</v>
       </c>
       <c r="M8" s="1">
         <v>320</v>
@@ -5864,7 +5864,7 @@
         <v>355</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>356</v>
@@ -5882,22 +5882,22 @@
         <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>295</v>
+        <v>359</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>362</v>
+        <v>298</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>363</v>
@@ -5909,10 +5909,10 @@
         <v>365</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>366</v>
@@ -5924,7 +5924,7 @@
         <v>368</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
@@ -5963,19 +5963,19 @@
         <v>48</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
@@ -5986,34 +5986,34 @@
         <v>9</v>
       </c>
       <c r="C12" s="1">
+        <v>113</v>
+      </c>
+      <c r="D12" s="1">
+        <v>102</v>
+      </c>
+      <c r="E12" s="1">
+        <v>98</v>
+      </c>
+      <c r="F12" s="1">
+        <v>101</v>
+      </c>
+      <c r="G12" s="1">
+        <v>414</v>
+      </c>
+      <c r="H12" s="1">
         <v>93</v>
       </c>
-      <c r="D12" s="1">
+      <c r="I12" s="1">
         <v>94</v>
       </c>
-      <c r="E12" s="1">
+      <c r="J12" s="1">
         <v>89</v>
       </c>
-      <c r="F12" s="1">
+      <c r="K12" s="1">
         <v>97</v>
       </c>
-      <c r="G12" s="1">
+      <c r="L12" s="1">
         <v>373</v>
-      </c>
-      <c r="H12" s="1">
-        <v>113</v>
-      </c>
-      <c r="I12" s="1">
-        <v>102</v>
-      </c>
-      <c r="J12" s="1">
-        <v>98</v>
-      </c>
-      <c r="K12" s="1">
-        <v>101</v>
-      </c>
-      <c r="L12" s="1">
-        <v>414</v>
       </c>
       <c r="M12" s="1">
         <v>206</v>
@@ -6100,7 +6100,7 @@
         <v>395</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>396</v>
@@ -6115,7 +6115,7 @@
         <v>399</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>400</v>
@@ -6130,7 +6130,7 @@
         <v>100</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
@@ -6169,19 +6169,19 @@
         <v>411</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
@@ -6192,34 +6192,34 @@
         <v>9</v>
       </c>
       <c r="C16" s="1">
+        <v>116</v>
+      </c>
+      <c r="D16" s="1">
+        <v>112</v>
+      </c>
+      <c r="E16" s="1">
+        <v>107</v>
+      </c>
+      <c r="F16" s="1">
+        <v>68</v>
+      </c>
+      <c r="G16" s="1">
+        <v>403</v>
+      </c>
+      <c r="H16" s="1">
         <v>114</v>
       </c>
-      <c r="D16" s="1">
+      <c r="I16" s="1">
         <v>114</v>
       </c>
-      <c r="E16" s="1">
+      <c r="J16" s="1">
         <v>112</v>
       </c>
-      <c r="F16" s="1">
+      <c r="K16" s="1">
         <v>94</v>
       </c>
-      <c r="G16" s="1">
+      <c r="L16" s="1">
         <v>434</v>
-      </c>
-      <c r="H16" s="1">
-        <v>116</v>
-      </c>
-      <c r="I16" s="1">
-        <v>112</v>
-      </c>
-      <c r="J16" s="1">
-        <v>107</v>
-      </c>
-      <c r="K16" s="1">
-        <v>68</v>
-      </c>
-      <c r="L16" s="1">
-        <v>403</v>
       </c>
       <c r="M16" s="1">
         <v>230</v>
@@ -6294,34 +6294,34 @@
         <v>26</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="I18" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>430</v>
-      </c>
       <c r="J18" s="1" t="s">
-        <v>431</v>
+        <v>264</v>
       </c>
       <c r="K18" s="1" t="s">
         <v>432</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>433</v>
@@ -6336,7 +6336,7 @@
         <v>436</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
@@ -6375,19 +6375,19 @@
         <v>444</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
@@ -6398,34 +6398,34 @@
         <v>9</v>
       </c>
       <c r="C20" s="1">
+        <v>64</v>
+      </c>
+      <c r="D20" s="1">
+        <v>65</v>
+      </c>
+      <c r="E20" s="1">
+        <v>68</v>
+      </c>
+      <c r="F20" s="1">
+        <v>71</v>
+      </c>
+      <c r="G20" s="1">
+        <v>268</v>
+      </c>
+      <c r="H20" s="1">
         <v>61</v>
       </c>
-      <c r="D20" s="1">
+      <c r="I20" s="1">
         <v>58</v>
       </c>
-      <c r="E20" s="1">
+      <c r="J20" s="1">
         <v>63</v>
       </c>
-      <c r="F20" s="1">
+      <c r="K20" s="1">
         <v>68</v>
       </c>
-      <c r="G20" s="1">
+      <c r="L20" s="1">
         <v>250</v>
-      </c>
-      <c r="H20" s="1">
-        <v>64</v>
-      </c>
-      <c r="I20" s="1">
-        <v>65</v>
-      </c>
-      <c r="J20" s="1">
-        <v>68</v>
-      </c>
-      <c r="K20" s="1">
-        <v>71</v>
-      </c>
-      <c r="L20" s="1">
-        <v>268</v>
       </c>
       <c r="M20" s="1">
         <v>125</v>
@@ -6461,25 +6461,25 @@
         <v>449</v>
       </c>
       <c r="G21" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="I21" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="J21" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="K21" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="L21" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="L21" s="1" t="s">
-        <v>453</v>
-      </c>
       <c r="M21" s="1" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="N21" s="1" t="s">
         <v>455</v>
@@ -6500,49 +6500,49 @@
         <v>26</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>399</v>
+        <v>459</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>459</v>
+        <v>334</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>393</v>
+        <v>460</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>460</v>
+        <v>67</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H22" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="I22" s="1" t="s">
-        <v>334</v>
-      </c>
       <c r="J22" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="K22" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="K22" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="L22" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="N22" s="1" t="s">
         <v>463</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
@@ -6581,19 +6581,19 @@
         <v>471</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
@@ -6604,34 +6604,34 @@
         <v>9</v>
       </c>
       <c r="C24" s="1">
+        <v>94</v>
+      </c>
+      <c r="D24" s="1">
+        <v>83</v>
+      </c>
+      <c r="E24" s="1">
+        <v>76</v>
+      </c>
+      <c r="F24" s="1">
+        <v>93</v>
+      </c>
+      <c r="G24" s="1">
+        <v>346</v>
+      </c>
+      <c r="H24" s="1">
         <v>82</v>
       </c>
-      <c r="D24" s="1">
+      <c r="I24" s="1">
         <v>79</v>
       </c>
-      <c r="E24" s="1">
+      <c r="J24" s="1">
         <v>79</v>
       </c>
-      <c r="F24" s="1">
+      <c r="K24" s="1">
         <v>79</v>
       </c>
-      <c r="G24" s="1">
+      <c r="L24" s="1">
         <v>319</v>
-      </c>
-      <c r="H24" s="1">
-        <v>94</v>
-      </c>
-      <c r="I24" s="1">
-        <v>83</v>
-      </c>
-      <c r="J24" s="1">
-        <v>76</v>
-      </c>
-      <c r="K24" s="1">
-        <v>93</v>
-      </c>
-      <c r="L24" s="1">
-        <v>346</v>
       </c>
       <c r="M24" s="1">
         <v>176</v>
@@ -6697,7 +6697,7 @@
         <v>486</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.3">
@@ -6712,43 +6712,43 @@
         <v>488</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>492</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>493</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="O26" s="1" t="s">
         <v>494</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
@@ -6787,19 +6787,19 @@
         <v>502</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.3">
@@ -6810,34 +6810,34 @@
         <v>9</v>
       </c>
       <c r="C28" s="1">
+        <v>197</v>
+      </c>
+      <c r="D28" s="1">
+        <v>207</v>
+      </c>
+      <c r="E28" s="1">
+        <v>208</v>
+      </c>
+      <c r="F28" s="1">
+        <v>178</v>
+      </c>
+      <c r="G28" s="1">
+        <v>790</v>
+      </c>
+      <c r="H28" s="1">
         <v>186</v>
       </c>
-      <c r="D28" s="1">
+      <c r="I28" s="1">
         <v>193</v>
       </c>
-      <c r="E28" s="1">
+      <c r="J28" s="1">
         <v>207</v>
       </c>
-      <c r="F28" s="1">
+      <c r="K28" s="1">
         <v>176</v>
       </c>
-      <c r="G28" s="1">
+      <c r="L28" s="1">
         <v>762</v>
-      </c>
-      <c r="H28" s="1">
-        <v>197</v>
-      </c>
-      <c r="I28" s="1">
-        <v>207</v>
-      </c>
-      <c r="J28" s="1">
-        <v>208</v>
-      </c>
-      <c r="K28" s="1">
-        <v>178</v>
-      </c>
-      <c r="L28" s="1">
-        <v>790</v>
       </c>
       <c r="M28" s="1">
         <v>383</v>
@@ -6864,31 +6864,31 @@
         <v>504</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="F29" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="G29" s="1" t="s">
         <v>507</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>508</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>17</v>
+        <v>509</v>
       </c>
       <c r="J29" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="L29" s="1" t="s">
         <v>509</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>511</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>512</v>
@@ -6897,10 +6897,10 @@
         <v>191</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="Q29" s="1" t="s">
         <v>513</v>
@@ -6912,34 +6912,34 @@
         <v>26</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>250</v>
+        <v>514</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>161</v>
+        <v>515</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>489</v>
+        <v>516</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>330</v>
+        <v>517</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>514</v>
+        <v>255</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>515</v>
+        <v>164</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>516</v>
+        <v>487</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>517</v>
+        <v>328</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>518</v>
@@ -6954,7 +6954,7 @@
         <v>520</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.3">
@@ -6993,19 +6993,19 @@
         <v>528</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.3">
@@ -7016,34 +7016,34 @@
         <v>9</v>
       </c>
       <c r="C32" s="1">
+        <v>253</v>
+      </c>
+      <c r="D32" s="1">
+        <v>251</v>
+      </c>
+      <c r="E32" s="1">
+        <v>255</v>
+      </c>
+      <c r="F32" s="1">
+        <v>208</v>
+      </c>
+      <c r="G32" s="1">
+        <v>967</v>
+      </c>
+      <c r="H32" s="1">
         <v>241</v>
       </c>
-      <c r="D32" s="1">
+      <c r="I32" s="1">
         <v>247</v>
       </c>
-      <c r="E32" s="1">
+      <c r="J32" s="1">
         <v>261</v>
       </c>
-      <c r="F32" s="1">
+      <c r="K32" s="1">
         <v>191</v>
       </c>
-      <c r="G32" s="1">
+      <c r="L32" s="1">
         <v>940</v>
-      </c>
-      <c r="H32" s="1">
-        <v>253</v>
-      </c>
-      <c r="I32" s="1">
-        <v>251</v>
-      </c>
-      <c r="J32" s="1">
-        <v>255</v>
-      </c>
-      <c r="K32" s="1">
-        <v>208</v>
-      </c>
-      <c r="L32" s="1">
-        <v>967</v>
       </c>
       <c r="M32" s="1">
         <v>494</v>
@@ -7067,25 +7067,25 @@
         <v>10</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>398</v>
+        <v>166</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>108</v>
+        <v>530</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>163</v>
+        <v>394</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>533</v>
+        <v>104</v>
       </c>
       <c r="J33" s="1" t="s">
         <v>534</v>
@@ -7097,7 +7097,7 @@
         <v>536</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="N33" s="1" t="s">
         <v>259</v>
@@ -7106,7 +7106,7 @@
         <v>537</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="Q33" s="1" t="s">
         <v>538</v>
@@ -7118,10 +7118,10 @@
         <v>26</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>91</v>
+        <v>435</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>199</v>
+        <v>270</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>539</v>
@@ -7130,13 +7130,13 @@
         <v>540</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>435</v>
+        <v>95</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>270</v>
+        <v>195</v>
       </c>
       <c r="J34" s="1" t="s">
         <v>541</v>
@@ -7145,7 +7145,7 @@
         <v>542</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>543</v>
@@ -7154,13 +7154,13 @@
         <v>302</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>544</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.3">
@@ -7199,19 +7199,19 @@
         <v>554</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.3">
@@ -7222,34 +7222,34 @@
         <v>9</v>
       </c>
       <c r="C36" s="1">
+        <v>1086</v>
+      </c>
+      <c r="D36" s="1">
+        <v>1074</v>
+      </c>
+      <c r="E36" s="1">
+        <v>1065</v>
+      </c>
+      <c r="F36" s="1">
+        <v>977</v>
+      </c>
+      <c r="G36" s="1">
+        <v>4202</v>
+      </c>
+      <c r="H36" s="1">
         <v>1018</v>
       </c>
-      <c r="D36" s="1">
+      <c r="I36" s="1">
         <v>1025</v>
       </c>
-      <c r="E36" s="1">
+      <c r="J36" s="1">
         <v>1061</v>
       </c>
-      <c r="F36" s="1">
+      <c r="K36" s="1">
         <v>943</v>
       </c>
-      <c r="G36" s="1">
+      <c r="L36" s="1">
         <v>4047</v>
-      </c>
-      <c r="H36" s="1">
-        <v>1086</v>
-      </c>
-      <c r="I36" s="1">
-        <v>1074</v>
-      </c>
-      <c r="J36" s="1">
-        <v>1065</v>
-      </c>
-      <c r="K36" s="1">
-        <v>977</v>
-      </c>
-      <c r="L36" s="1">
-        <v>4202</v>
       </c>
       <c r="M36" s="1">
         <v>2104</v>
@@ -7273,49 +7273,49 @@
         <v>10</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.3">
@@ -7327,22 +7327,22 @@
         <v>160</v>
       </c>
       <c r="D38" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="F38" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="G38" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="G38" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H38" s="1" t="s">
+      <c r="I38" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="J38" s="1" t="s">
         <v>165</v>
@@ -7351,7 +7351,7 @@
         <v>166</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M38" s="1" t="s">
         <v>167</v>
@@ -7366,7 +7366,7 @@
         <v>170</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.3">
@@ -7405,19 +7405,19 @@
         <v>123</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q39" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.3">
@@ -7634,34 +7634,34 @@
         <v>9</v>
       </c>
       <c r="C4" s="1">
+        <v>130</v>
+      </c>
+      <c r="D4" s="1">
+        <v>121</v>
+      </c>
+      <c r="E4" s="1">
+        <v>99</v>
+      </c>
+      <c r="F4" s="1">
+        <v>83</v>
+      </c>
+      <c r="G4" s="1">
+        <v>433</v>
+      </c>
+      <c r="H4" s="1">
         <v>136</v>
       </c>
-      <c r="D4" s="1">
+      <c r="I4" s="1">
         <v>134</v>
       </c>
-      <c r="E4" s="1">
+      <c r="J4" s="1">
         <v>89</v>
       </c>
-      <c r="F4" s="1">
+      <c r="K4" s="1">
         <v>69</v>
       </c>
-      <c r="G4" s="1">
+      <c r="L4" s="1">
         <v>428</v>
-      </c>
-      <c r="H4" s="1">
-        <v>130</v>
-      </c>
-      <c r="I4" s="1">
-        <v>121</v>
-      </c>
-      <c r="J4" s="1">
-        <v>99</v>
-      </c>
-      <c r="K4" s="1">
-        <v>83</v>
-      </c>
-      <c r="L4" s="1">
-        <v>433</v>
       </c>
       <c r="M4" s="1">
         <v>266</v>
@@ -7691,13 +7691,13 @@
         <v>557</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>380</v>
+        <v>558</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>559</v>
+        <v>326</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>560</v>
@@ -7706,13 +7706,13 @@
         <v>561</v>
       </c>
       <c r="J5" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>563</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>326</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>564</v>
@@ -7727,7 +7727,7 @@
         <v>567</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
@@ -7748,7 +7748,7 @@
         <v>571</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>572</v>
@@ -7763,7 +7763,7 @@
         <v>575</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>576</v>
@@ -7778,7 +7778,7 @@
         <v>579</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
@@ -7817,19 +7817,19 @@
         <v>589</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
@@ -7840,34 +7840,34 @@
         <v>9</v>
       </c>
       <c r="C8" s="1">
+        <v>719</v>
+      </c>
+      <c r="D8" s="1">
+        <v>708</v>
+      </c>
+      <c r="E8" s="1">
+        <v>695</v>
+      </c>
+      <c r="F8" s="1">
+        <v>656</v>
+      </c>
+      <c r="G8" s="1">
+        <v>2778</v>
+      </c>
+      <c r="H8" s="1">
         <v>628</v>
       </c>
-      <c r="D8" s="1">
+      <c r="I8" s="1">
         <v>655</v>
       </c>
-      <c r="E8" s="1">
+      <c r="J8" s="1">
         <v>714</v>
       </c>
-      <c r="F8" s="1">
+      <c r="K8" s="1">
         <v>643</v>
       </c>
-      <c r="G8" s="1">
+      <c r="L8" s="1">
         <v>2640</v>
-      </c>
-      <c r="H8" s="1">
-        <v>719</v>
-      </c>
-      <c r="I8" s="1">
-        <v>708</v>
-      </c>
-      <c r="J8" s="1">
-        <v>695</v>
-      </c>
-      <c r="K8" s="1">
-        <v>656</v>
-      </c>
-      <c r="L8" s="1">
-        <v>2778</v>
       </c>
       <c r="M8" s="1">
         <v>1347</v>
@@ -7927,7 +7927,7 @@
         <v>602</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>603</v>
@@ -7945,31 +7945,31 @@
         <v>605</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>92</v>
+        <v>606</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>70</v>
+        <v>607</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>288</v>
+        <v>254</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>607</v>
+        <v>96</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>608</v>
+        <v>66</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>249</v>
+        <v>285</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>609</v>
@@ -7978,13 +7978,13 @@
         <v>100</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>610</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
@@ -8023,19 +8023,19 @@
         <v>620</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
@@ -8046,34 +8046,34 @@
         <v>9</v>
       </c>
       <c r="C12" s="1">
+        <v>236</v>
+      </c>
+      <c r="D12" s="1">
+        <v>244</v>
+      </c>
+      <c r="E12" s="1">
+        <v>271</v>
+      </c>
+      <c r="F12" s="1">
+        <v>238</v>
+      </c>
+      <c r="G12" s="1">
+        <v>989</v>
+      </c>
+      <c r="H12" s="1">
         <v>254</v>
       </c>
-      <c r="D12" s="1">
+      <c r="I12" s="1">
         <v>236</v>
       </c>
-      <c r="E12" s="1">
+      <c r="J12" s="1">
         <v>258</v>
       </c>
-      <c r="F12" s="1">
+      <c r="K12" s="1">
         <v>230</v>
       </c>
-      <c r="G12" s="1">
+      <c r="L12" s="1">
         <v>978</v>
-      </c>
-      <c r="H12" s="1">
-        <v>236</v>
-      </c>
-      <c r="I12" s="1">
-        <v>244</v>
-      </c>
-      <c r="J12" s="1">
-        <v>271</v>
-      </c>
-      <c r="K12" s="1">
-        <v>238</v>
-      </c>
-      <c r="L12" s="1">
-        <v>989</v>
       </c>
       <c r="M12" s="1">
         <v>490</v>
@@ -8097,37 +8097,37 @@
         <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="J13" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="L13" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>626</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>627</v>
-      </c>
       <c r="M13" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>628</v>
@@ -8136,7 +8136,7 @@
         <v>629</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Q13" s="1" t="s">
         <v>260</v>
@@ -8148,10 +8148,10 @@
         <v>26</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>67</v>
+        <v>398</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>196</v>
+        <v>127</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>630</v>
@@ -8160,13 +8160,13 @@
         <v>631</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>394</v>
+        <v>71</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>132</v>
+        <v>200</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>632</v>
@@ -8175,22 +8175,22 @@
         <v>633</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>634</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="O14" s="1" t="s">
         <v>635</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
@@ -8229,19 +8229,19 @@
         <v>340</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
@@ -8252,34 +8252,34 @@
         <v>9</v>
       </c>
       <c r="C16" s="1">
+        <v>1085</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1073</v>
+      </c>
+      <c r="E16" s="1">
+        <v>1065</v>
+      </c>
+      <c r="F16" s="1">
+        <v>977</v>
+      </c>
+      <c r="G16" s="1">
+        <v>4200</v>
+      </c>
+      <c r="H16" s="1">
         <v>1018</v>
       </c>
-      <c r="D16" s="1">
+      <c r="I16" s="1">
         <v>1025</v>
       </c>
-      <c r="E16" s="1">
+      <c r="J16" s="1">
         <v>1061</v>
       </c>
-      <c r="F16" s="1">
+      <c r="K16" s="1">
         <v>942</v>
       </c>
-      <c r="G16" s="1">
+      <c r="L16" s="1">
         <v>4046</v>
-      </c>
-      <c r="H16" s="1">
-        <v>1085</v>
-      </c>
-      <c r="I16" s="1">
-        <v>1073</v>
-      </c>
-      <c r="J16" s="1">
-        <v>1065</v>
-      </c>
-      <c r="K16" s="1">
-        <v>977</v>
-      </c>
-      <c r="L16" s="1">
-        <v>4200</v>
       </c>
       <c r="M16" s="1">
         <v>2103</v>
@@ -8303,49 +8303,49 @@
         <v>10</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
@@ -8354,34 +8354,34 @@
         <v>26</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="F18" s="1" t="s">
+      <c r="I18" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>643</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="L18" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>644</v>
@@ -8396,7 +8396,7 @@
         <v>647</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
@@ -8435,19 +8435,19 @@
         <v>653</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
@@ -8659,34 +8659,34 @@
         <v>9</v>
       </c>
       <c r="C4" s="1">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="D4" s="1">
         <v>130</v>
       </c>
       <c r="E4" s="1">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="F4" s="1">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="G4" s="1">
-        <v>566</v>
+        <v>592</v>
       </c>
       <c r="H4" s="1">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I4" s="1">
         <v>130</v>
       </c>
       <c r="J4" s="1">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="K4" s="1">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="L4" s="1">
-        <v>592</v>
+        <v>566</v>
       </c>
       <c r="M4" s="1">
         <v>299</v>
@@ -8773,7 +8773,7 @@
         <v>673</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>674</v>
@@ -8788,7 +8788,7 @@
         <v>677</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>678</v>
@@ -8803,7 +8803,7 @@
         <v>681</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
@@ -8842,19 +8842,19 @@
         <v>685</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
@@ -8868,31 +8868,31 @@
         <v>130</v>
       </c>
       <c r="D8" s="1">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E8" s="1">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="F8" s="1">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="G8" s="1">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="H8" s="1">
         <v>130</v>
       </c>
       <c r="I8" s="1">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="J8" s="1">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="K8" s="1">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="L8" s="1">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="M8" s="1">
         <v>260</v>
@@ -8967,37 +8967,37 @@
         <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>359</v>
-      </c>
       <c r="G10" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>671</v>
+        <v>705</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>707</v>
+        <v>363</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>708</v>
@@ -9009,7 +9009,7 @@
         <v>710</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
@@ -9048,19 +9048,19 @@
         <v>714</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
@@ -9071,34 +9071,34 @@
         <v>9</v>
       </c>
       <c r="C12" s="1">
+        <v>148</v>
+      </c>
+      <c r="D12" s="1">
+        <v>125</v>
+      </c>
+      <c r="E12" s="1">
+        <v>111</v>
+      </c>
+      <c r="F12" s="1">
+        <v>84</v>
+      </c>
+      <c r="G12" s="1">
+        <v>468</v>
+      </c>
+      <c r="H12" s="1">
         <v>101</v>
       </c>
-      <c r="D12" s="1">
+      <c r="I12" s="1">
         <v>126</v>
       </c>
-      <c r="E12" s="1">
+      <c r="J12" s="1">
         <v>95</v>
       </c>
-      <c r="F12" s="1">
+      <c r="K12" s="1">
         <v>75</v>
       </c>
-      <c r="G12" s="1">
+      <c r="L12" s="1">
         <v>397</v>
-      </c>
-      <c r="H12" s="1">
-        <v>148</v>
-      </c>
-      <c r="I12" s="1">
-        <v>125</v>
-      </c>
-      <c r="J12" s="1">
-        <v>111</v>
-      </c>
-      <c r="K12" s="1">
-        <v>84</v>
-      </c>
-      <c r="L12" s="1">
-        <v>468</v>
       </c>
       <c r="M12" s="1">
         <v>249</v>
@@ -9131,7 +9131,7 @@
         <v>718</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>473</v>
+        <v>317</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>719</v>
@@ -9146,7 +9146,7 @@
         <v>722</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>322</v>
+        <v>478</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>723</v>
@@ -9173,34 +9173,34 @@
         <v>26</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>645</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>728</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>729</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>730</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>731</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>732</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>733</v>
@@ -9215,7 +9215,7 @@
         <v>736</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
@@ -9254,19 +9254,19 @@
         <v>744</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
@@ -9277,34 +9277,34 @@
         <v>9</v>
       </c>
       <c r="C16" s="1">
+        <v>304</v>
+      </c>
+      <c r="D16" s="1">
+        <v>324</v>
+      </c>
+      <c r="E16" s="1">
+        <v>301</v>
+      </c>
+      <c r="F16" s="1">
+        <v>285</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1214</v>
+      </c>
+      <c r="H16" s="1">
         <v>303</v>
       </c>
-      <c r="D16" s="1">
+      <c r="I16" s="1">
         <v>299</v>
       </c>
-      <c r="E16" s="1">
+      <c r="J16" s="1">
         <v>341</v>
       </c>
-      <c r="F16" s="1">
+      <c r="K16" s="1">
         <v>278</v>
       </c>
-      <c r="G16" s="1">
+      <c r="L16" s="1">
         <v>1221</v>
-      </c>
-      <c r="H16" s="1">
-        <v>304</v>
-      </c>
-      <c r="I16" s="1">
-        <v>324</v>
-      </c>
-      <c r="J16" s="1">
-        <v>301</v>
-      </c>
-      <c r="K16" s="1">
-        <v>285</v>
-      </c>
-      <c r="L16" s="1">
-        <v>1214</v>
       </c>
       <c r="M16" s="1">
         <v>607</v>
@@ -9379,49 +9379,49 @@
         <v>26</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>760</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>676</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>761</v>
       </c>
       <c r="F18" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>359</v>
-      </c>
       <c r="I18" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="J18" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="K18" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="K18" s="1" t="s">
-        <v>328</v>
-      </c>
       <c r="L18" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>765</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>538</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
@@ -9460,19 +9460,19 @@
         <v>773</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
@@ -9483,34 +9483,34 @@
         <v>9</v>
       </c>
       <c r="C20" s="1">
+        <v>192</v>
+      </c>
+      <c r="D20" s="1">
+        <v>197</v>
+      </c>
+      <c r="E20" s="1">
+        <v>198</v>
+      </c>
+      <c r="F20" s="1">
+        <v>198</v>
+      </c>
+      <c r="G20" s="1">
+        <v>785</v>
+      </c>
+      <c r="H20" s="1">
         <v>156</v>
       </c>
-      <c r="D20" s="1">
+      <c r="I20" s="1">
         <v>213</v>
       </c>
-      <c r="E20" s="1">
+      <c r="J20" s="1">
         <v>206</v>
       </c>
-      <c r="F20" s="1">
+      <c r="K20" s="1">
         <v>180</v>
       </c>
-      <c r="G20" s="1">
+      <c r="L20" s="1">
         <v>755</v>
-      </c>
-      <c r="H20" s="1">
-        <v>192</v>
-      </c>
-      <c r="I20" s="1">
-        <v>197</v>
-      </c>
-      <c r="J20" s="1">
-        <v>198</v>
-      </c>
-      <c r="K20" s="1">
-        <v>198</v>
-      </c>
-      <c r="L20" s="1">
-        <v>785</v>
       </c>
       <c r="M20" s="1">
         <v>348</v>
@@ -9534,37 +9534,37 @@
         <v>10</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>777</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>436</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>778</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>507</v>
+        <v>779</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>781</v>
+        <v>436</v>
       </c>
       <c r="L21" s="1" t="s">
         <v>782</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="N21" s="1" t="s">
         <v>783</v>
@@ -9576,7 +9576,7 @@
         <v>785</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
@@ -9594,10 +9594,10 @@
         <v>788</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>254</v>
+        <v>788</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>789</v>
@@ -9609,10 +9609,10 @@
         <v>791</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>791</v>
+        <v>249</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>792</v>
@@ -9627,7 +9627,7 @@
         <v>795</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
@@ -9666,19 +9666,19 @@
         <v>496</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
@@ -9689,34 +9689,34 @@
         <v>9</v>
       </c>
       <c r="C24" s="1">
+        <v>109</v>
+      </c>
+      <c r="D24" s="1">
+        <v>107</v>
+      </c>
+      <c r="E24" s="1">
+        <v>97</v>
+      </c>
+      <c r="F24" s="1">
+        <v>90</v>
+      </c>
+      <c r="G24" s="1">
+        <v>403</v>
+      </c>
+      <c r="H24" s="1">
         <v>110</v>
       </c>
-      <c r="D24" s="1">
+      <c r="I24" s="1">
         <v>76</v>
       </c>
-      <c r="E24" s="1">
+      <c r="J24" s="1">
         <v>89</v>
       </c>
-      <c r="F24" s="1">
+      <c r="K24" s="1">
         <v>99</v>
       </c>
-      <c r="G24" s="1">
+      <c r="L24" s="1">
         <v>374</v>
-      </c>
-      <c r="H24" s="1">
-        <v>109</v>
-      </c>
-      <c r="I24" s="1">
-        <v>107</v>
-      </c>
-      <c r="J24" s="1">
-        <v>97</v>
-      </c>
-      <c r="K24" s="1">
-        <v>90</v>
-      </c>
-      <c r="L24" s="1">
-        <v>403</v>
       </c>
       <c r="M24" s="1">
         <v>219</v>
@@ -9746,25 +9746,25 @@
         <v>804</v>
       </c>
       <c r="E25" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="H25" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="I25" s="1" t="s">
         <v>807</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="J25" s="1" t="s">
         <v>808</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="K25" s="1" t="s">
         <v>809</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>718</v>
       </c>
       <c r="L25" s="1" t="s">
         <v>810</v>
@@ -9773,7 +9773,7 @@
         <v>811</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="O25" s="1" t="s">
         <v>812</v>
@@ -9791,49 +9791,49 @@
         <v>26</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>815</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="E26" s="1" t="s">
+      <c r="G26" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H26" s="1" t="s">
         <v>816</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="I26" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="K26" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="G26" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>817</v>
-      </c>
       <c r="L26" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>818</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
@@ -9872,19 +9872,19 @@
         <v>826</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.3">
@@ -9895,34 +9895,34 @@
         <v>9</v>
       </c>
       <c r="C28" s="1">
+        <v>1029</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1023</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1017</v>
+      </c>
+      <c r="F28" s="1">
+        <v>959</v>
+      </c>
+      <c r="G28" s="1">
+        <v>4028</v>
+      </c>
+      <c r="H28" s="1">
         <v>953</v>
       </c>
-      <c r="D28" s="1">
+      <c r="I28" s="1">
         <v>980</v>
       </c>
-      <c r="E28" s="1">
+      <c r="J28" s="1">
         <v>1013</v>
       </c>
-      <c r="F28" s="1">
+      <c r="K28" s="1">
         <v>930</v>
       </c>
-      <c r="G28" s="1">
+      <c r="L28" s="1">
         <v>3876</v>
-      </c>
-      <c r="H28" s="1">
-        <v>1029</v>
-      </c>
-      <c r="I28" s="1">
-        <v>1023</v>
-      </c>
-      <c r="J28" s="1">
-        <v>1017</v>
-      </c>
-      <c r="K28" s="1">
-        <v>959</v>
-      </c>
-      <c r="L28" s="1">
-        <v>4028</v>
       </c>
       <c r="M28" s="1">
         <v>1982</v>
@@ -9946,49 +9946,49 @@
         <v>10</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.3">
@@ -9997,40 +9997,40 @@
         <v>26</v>
       </c>
       <c r="C30" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>827</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>828</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="F30" s="1" t="s">
         <v>829</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>490</v>
-      </c>
       <c r="G30" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>643</v>
+        <v>830</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>832</v>
+        <v>488</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>833</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="O30" s="1" t="s">
         <v>834</v>
@@ -10039,7 +10039,7 @@
         <v>835</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.3">
@@ -10078,19 +10078,19 @@
         <v>839</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.3">
@@ -10195,7 +10195,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94CBF94-6F84-4122-A98A-43DFFF11C3E7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01DD6714-A335-4BF5-ADC3-37EA214564D2}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
